--- a/mortality_odds_all.xlsx
+++ b/mortality_odds_all.xlsx
@@ -39,16 +39,16 @@
     <t>io_mono</t>
   </si>
   <si>
-    <t>firstlinechemotherapy</t>
+    <t>firstlinechemothe~y</t>
   </si>
   <si>
-    <t>nonfirstlinechemotherapy</t>
+    <t>nonfirstlinechemo~y</t>
   </si>
   <si>
-    <t>otherfirstlinetherapy</t>
+    <t>otherfirstlinethe~y</t>
   </si>
   <si>
-    <t>firstlinecombinationtherapy</t>
+    <t>firstlinecombinat~y</t>
   </si>
   <si>
     <t>antibrafdrug</t>
@@ -60,10 +60,10 @@
     <t>metinhibitor</t>
   </si>
   <si>
-    <t>carboplatinmonotherapy</t>
+    <t>carboplatinmonoth~y</t>
   </si>
   <si>
-    <t>cisplatinmonotherapy</t>
+    <t>cisplatinmonother~y</t>
   </si>
   <si>
     <t>antialkdrug#alk</t>
@@ -105,10 +105,10 @@
     <t>ecog4</t>
   </si>
   <si>
-    <t>squamouscellcarcinoma</t>
+    <t>squamouscellcarci~a</t>
   </si>
   <si>
-    <t>nonsquamouscellcarcinoma</t>
+    <t>nonsquamouscellca~a</t>
   </si>
   <si>
     <t>pdl1</t>
@@ -141,13 +141,13 @@
     <t>male</t>
   </si>
   <si>
-    <t>daysfromadvanceddiagnosistotreat</t>
+    <t>daysfromadvancedd~t</t>
   </si>
   <si>
-    <t>patientassistanceprogram</t>
+    <t>patientassistance~m</t>
   </si>
   <si>
-    <t>othergovernmentalinsurance</t>
+    <t>othergovernmental~e</t>
   </si>
   <si>
     <t>medicare</t>
@@ -159,7 +159,7 @@
     <t>medicaid</t>
   </si>
   <si>
-    <t>commercialhealthplan</t>
+    <t>commercialhealthp~n</t>
   </si>
   <si>
     <t>noinsurance</t>
@@ -189,7 +189,7 @@
     <t>neversmoker</t>
   </si>
   <si>
-    <t>academicmedicalcenter</t>
+    <t>academicmedicalce~r</t>
   </si>
   <si>
     <t>kidney_bool</t>
@@ -198,10 +198,10 @@
     <t>liver_bool</t>
   </si>
   <si>
-    <t>connective_tissue_bool</t>
+    <t>connective_tissue~l</t>
   </si>
   <si>
-    <t>interstitiallungdisease</t>
+    <t>interstitiallungd~e</t>
   </si>
   <si>
     <t>diabetes</t>
@@ -216,28 +216,28 @@
     <t>othercnsmetastases</t>
   </si>
   <si>
-    <t>digestivesystemmetastases</t>
+    <t>digestivesystemme~s</t>
   </si>
   <si>
     <t>adrenalmetastases</t>
   </si>
   <si>
-    <t>unspecifiedmetastases</t>
+    <t>unspecifiedmetast~s</t>
   </si>
   <si>
-    <t>antiinfectiveusepriortotreatment</t>
+    <t>antiinfectiveusep~t</t>
   </si>
   <si>
-    <t>glucocorticoidusepriortotreatmen</t>
+    <t>glucocorticoiduse~n</t>
   </si>
   <si>
-    <t>clinicalstudydrugused</t>
+    <t>clinicalstudydrug~d</t>
   </si>
   <si>
     <t>bevacizumabused</t>
   </si>
   <si>
-    <t>threeormorechemotherapydrugs</t>
+    <t>threeormorechemot~s</t>
   </si>
   <si>
     <t>pdl1reported</t>

--- a/mortality_odds_all.xlsx
+++ b/mortality_odds_all.xlsx
@@ -39,16 +39,16 @@
     <t>io_mono</t>
   </si>
   <si>
-    <t>firstlinechemothe~y</t>
+    <t>firstlinechemotherapy</t>
   </si>
   <si>
-    <t>nonfirstlinechemo~y</t>
+    <t>nonfirstlinechemotherapy</t>
   </si>
   <si>
-    <t>otherfirstlinethe~y</t>
+    <t>otherfirstlinetherapy</t>
   </si>
   <si>
-    <t>firstlinecombinat~y</t>
+    <t>firstlinecombinationtherapy</t>
   </si>
   <si>
     <t>antibrafdrug</t>
@@ -60,10 +60,10 @@
     <t>metinhibitor</t>
   </si>
   <si>
-    <t>carboplatinmonoth~y</t>
+    <t>carboplatinmonotherapy</t>
   </si>
   <si>
-    <t>cisplatinmonother~y</t>
+    <t>cisplatinmonotherapy</t>
   </si>
   <si>
     <t>antialkdrug#alk</t>
@@ -105,10 +105,10 @@
     <t>ecog4</t>
   </si>
   <si>
-    <t>squamouscellcarci~a</t>
+    <t>squamouscellcarcinoma</t>
   </si>
   <si>
-    <t>nonsquamouscellca~a</t>
+    <t>nonsquamouscellcarcinoma</t>
   </si>
   <si>
     <t>pdl1</t>
@@ -141,13 +141,13 @@
     <t>male</t>
   </si>
   <si>
-    <t>daysfromadvancedd~t</t>
+    <t>daysfromadvanceddiagnosistotreat</t>
   </si>
   <si>
-    <t>patientassistance~m</t>
+    <t>patientassistanceprogram</t>
   </si>
   <si>
-    <t>othergovernmental~e</t>
+    <t>othergovernmentalinsurance</t>
   </si>
   <si>
     <t>medicare</t>
@@ -159,7 +159,7 @@
     <t>medicaid</t>
   </si>
   <si>
-    <t>commercialhealthp~n</t>
+    <t>commercialhealthplan</t>
   </si>
   <si>
     <t>noinsurance</t>
@@ -189,7 +189,7 @@
     <t>neversmoker</t>
   </si>
   <si>
-    <t>academicmedicalce~r</t>
+    <t>academicmedicalcenter</t>
   </si>
   <si>
     <t>kidney_bool</t>
@@ -198,10 +198,10 @@
     <t>liver_bool</t>
   </si>
   <si>
-    <t>connective_tissue~l</t>
+    <t>connective_tissue_bool</t>
   </si>
   <si>
-    <t>interstitiallungd~e</t>
+    <t>interstitiallungdisease</t>
   </si>
   <si>
     <t>diabetes</t>
@@ -216,28 +216,28 @@
     <t>othercnsmetastases</t>
   </si>
   <si>
-    <t>digestivesystemme~s</t>
+    <t>digestivesystemmetastases</t>
   </si>
   <si>
     <t>adrenalmetastases</t>
   </si>
   <si>
-    <t>unspecifiedmetast~s</t>
+    <t>unspecifiedmetastases</t>
   </si>
   <si>
-    <t>antiinfectiveusep~t</t>
+    <t>antiinfectiveusepriortotreatment</t>
   </si>
   <si>
-    <t>glucocorticoiduse~n</t>
+    <t>glucocorticoidusepriortotreatmen</t>
   </si>
   <si>
-    <t>clinicalstudydrug~d</t>
+    <t>clinicalstudydrugused</t>
   </si>
   <si>
     <t>bevacizumabused</t>
   </si>
   <si>
-    <t>threeormorechemot~s</t>
+    <t>threeormorechemotherapydrugs</t>
   </si>
   <si>
     <t>pdl1reported</t>

--- a/mortality_odds_all.xlsx
+++ b/mortality_odds_all.xlsx
@@ -10233,22 +10233,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="25">
-        <v>1.4714860000000001</v>
+        <v>3.8267310000000001</v>
       </c>
       <c r="C2" s="26">
-        <v>0.27750019999999997</v>
+        <v>4.3730690000000001</v>
       </c>
       <c r="D2" s="27">
-        <v>2.0499999999999998</v>
+        <v>1.1699999999999999</v>
       </c>
       <c r="E2" s="28">
-        <v>0.041000000000000002</v>
+        <v>0.23999999999999999</v>
       </c>
       <c r="F2" s="29">
-        <v>1.0167930000000001</v>
+        <v>0.40747529999999999</v>
       </c>
       <c r="G2" s="30">
-        <v>2.1295120000000001</v>
+        <v>35.93806</v>
       </c>
     </row>
     <row r="3">
@@ -10256,22 +10256,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="33">
-        <v>1.226254</v>
+        <v>0.85448279999999999</v>
       </c>
       <c r="C3" s="34">
-        <v>0.22594320000000001</v>
+        <v>0.044570100000000001</v>
       </c>
       <c r="D3" s="35">
-        <v>1.1100000000000001</v>
+        <v>-3.0099999999999998</v>
       </c>
       <c r="E3" s="36">
-        <v>0.26800000000000002</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="F3" s="37">
-        <v>0.85455999999999999</v>
+        <v>0.77144400000000002</v>
       </c>
       <c r="G3" s="38">
-        <v>1.7596179999999999</v>
+        <v>0.94646010000000003</v>
       </c>
     </row>
     <row r="4">
@@ -10279,22 +10279,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="41">
-        <v>2.0235910000000001</v>
+        <v>1.4093929999999999</v>
       </c>
       <c r="C4" s="42">
-        <v>0.3911288</v>
+        <v>0.10929759999999999</v>
       </c>
       <c r="D4" s="43">
-        <v>3.6499999999999999</v>
+        <v>4.4299999999999997</v>
       </c>
       <c r="E4" s="44">
         <v>0</v>
       </c>
       <c r="F4" s="45">
-        <v>1.385475</v>
+        <v>1.2106589999999999</v>
       </c>
       <c r="G4" s="46">
-        <v>2.9556079999999998</v>
+        <v>1.640749</v>
       </c>
     </row>
     <row r="5">
@@ -10302,22 +10302,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="49">
-        <v>1.1918010000000001</v>
+        <v>0.83954700000000004</v>
       </c>
       <c r="C5" s="50">
-        <v>0.2200386</v>
+        <v>0.059070400000000002</v>
       </c>
       <c r="D5" s="51">
-        <v>0.94999999999999996</v>
+        <v>-2.4900000000000002</v>
       </c>
       <c r="E5" s="52">
-        <v>0.34200000000000003</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="F5" s="53">
-        <v>0.82994460000000003</v>
+        <v>0.73139949999999998</v>
       </c>
       <c r="G5" s="54">
-        <v>1.711428</v>
+        <v>0.96368569999999998</v>
       </c>
     </row>
     <row r="6">
@@ -10325,22 +10325,22 @@
         <v>11</v>
       </c>
       <c r="B6" s="57">
-        <v>1.208744</v>
+        <v>0.2195956</v>
       </c>
       <c r="C6" s="58">
-        <v>0.22718530000000001</v>
+        <v>0.25078820000000002</v>
       </c>
       <c r="D6" s="59">
-        <v>1.01</v>
+        <v>-1.3300000000000001</v>
       </c>
       <c r="E6" s="60">
-        <v>0.313</v>
+        <v>0.184</v>
       </c>
       <c r="F6" s="61">
-        <v>0.83627649999999998</v>
+        <v>0.023415999999999999</v>
       </c>
       <c r="G6" s="62">
-        <v>1.7471049999999999</v>
+        <v>2.0593710000000001</v>
       </c>
     </row>
     <row r="7">
@@ -10348,22 +10348,22 @@
         <v>12</v>
       </c>
       <c r="B7" s="65">
-        <v>1.242551</v>
+        <v>0.90177779999999996</v>
       </c>
       <c r="C7" s="66">
-        <v>0.4269772</v>
+        <v>0.26817350000000001</v>
       </c>
       <c r="D7" s="67">
-        <v>0.63</v>
+        <v>-0.34999999999999998</v>
       </c>
       <c r="E7" s="68">
-        <v>0.52700000000000002</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="F7" s="69">
-        <v>0.63360190000000005</v>
+        <v>0.50346190000000002</v>
       </c>
       <c r="G7" s="70">
-        <v>2.4367570000000001</v>
+        <v>1.6152230000000001</v>
       </c>
     </row>
     <row r="8">
@@ -10371,22 +10371,22 @@
         <v>13</v>
       </c>
       <c r="B8" s="73">
-        <v>0.84171430000000003</v>
+        <v>0.67965509999999996</v>
       </c>
       <c r="C8" s="74">
-        <v>0.66602050000000002</v>
+        <v>0.52324990000000005</v>
       </c>
       <c r="D8" s="75">
-        <v>-0.22</v>
+        <v>-0.5</v>
       </c>
       <c r="E8" s="76">
-        <v>0.82799999999999996</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="F8" s="77">
-        <v>0.17849960000000001</v>
+        <v>0.15030350000000001</v>
       </c>
       <c r="G8" s="78">
-        <v>3.9691010000000002</v>
+        <v>3.073321</v>
       </c>
     </row>
     <row r="9">
@@ -10394,22 +10394,22 @@
         <v>14</v>
       </c>
       <c r="B9" s="81">
-        <v>0.31065199999999998</v>
+        <v>0.21361069999999999</v>
       </c>
       <c r="C9" s="82">
-        <v>0.33587640000000002</v>
+        <v>0.2276011</v>
       </c>
       <c r="D9" s="83">
-        <v>-1.0800000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="E9" s="84">
-        <v>0.28000000000000003</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="F9" s="85">
-        <v>0.037321300000000002</v>
+        <v>0.026464999999999999</v>
       </c>
       <c r="G9" s="86">
-        <v>2.5857809999999999</v>
+        <v>1.724145</v>
       </c>
     </row>
     <row r="10">
@@ -10417,22 +10417,22 @@
         <v>15</v>
       </c>
       <c r="B10" s="89">
-        <v>0.76205319999999999</v>
+        <v>0.5302654</v>
       </c>
       <c r="C10" s="90">
-        <v>0.21710789999999999</v>
+        <v>0.1181931</v>
       </c>
       <c r="D10" s="91">
-        <v>-0.94999999999999996</v>
+        <v>-2.8500000000000001</v>
       </c>
       <c r="E10" s="92">
-        <v>0.34000000000000002</v>
+        <v>0.0040000000000000001</v>
       </c>
       <c r="F10" s="93">
-        <v>0.43599260000000001</v>
+        <v>0.34258260000000001</v>
       </c>
       <c r="G10" s="94">
-        <v>1.331961</v>
+        <v>0.82076959999999999</v>
       </c>
     </row>
     <row r="11">
@@ -10440,22 +10440,22 @@
         <v>16</v>
       </c>
       <c r="B11" s="97">
-        <v>1.158396</v>
+        <v>0.8067571</v>
       </c>
       <c r="C11" s="98">
-        <v>0.56470209999999999</v>
+        <v>0.36643559999999997</v>
       </c>
       <c r="D11" s="99">
-        <v>0.29999999999999999</v>
+        <v>-0.46999999999999997</v>
       </c>
       <c r="E11" s="100">
-        <v>0.76300000000000001</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="F11" s="101">
-        <v>0.44556210000000002</v>
+        <v>0.33122279999999998</v>
       </c>
       <c r="G11" s="102">
-        <v>3.0116610000000001</v>
+        <v>1.9650129999999999</v>
       </c>
     </row>
     <row r="12">
@@ -10509,22 +10509,22 @@
         <v>18</v>
       </c>
       <c r="B14" s="121">
-        <v>0.4470266</v>
+        <v>0.44733289999999998</v>
       </c>
       <c r="C14" s="122">
-        <v>0.061254400000000001</v>
+        <v>0.061317200000000002</v>
       </c>
       <c r="D14" s="123">
-        <v>-5.8799999999999999</v>
+        <v>-5.8700000000000001</v>
       </c>
       <c r="E14" s="124">
         <v>0</v>
       </c>
       <c r="F14" s="125">
-        <v>0.3417404</v>
+        <v>0.34194350000000001</v>
       </c>
       <c r="G14" s="126">
-        <v>0.5847502</v>
+        <v>0.58520419999999995</v>
       </c>
     </row>
     <row r="15">
@@ -10532,22 +10532,22 @@
         <v>19</v>
       </c>
       <c r="B15" s="129">
-        <v>0.40945949999999998</v>
+        <v>0.2914735</v>
       </c>
       <c r="C15" s="130">
-        <v>0.44564229999999999</v>
+        <v>0.31455850000000002</v>
       </c>
       <c r="D15" s="131">
-        <v>-0.81999999999999995</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="E15" s="132">
-        <v>0.41199999999999998</v>
+        <v>0.253</v>
       </c>
       <c r="F15" s="133">
-        <v>0.0485055</v>
+        <v>0.035154499999999998</v>
       </c>
       <c r="G15" s="134">
-        <v>3.4564539999999999</v>
+        <v>2.4166669999999999</v>
       </c>
     </row>
     <row r="16">
@@ -10555,22 +10555,22 @@
         <v>20</v>
       </c>
       <c r="B16" s="137">
-        <v>0.25979469999999999</v>
+        <v>0.1848786</v>
       </c>
       <c r="C16" s="138">
-        <v>0.077159800000000001</v>
+        <v>0.045136200000000001</v>
       </c>
       <c r="D16" s="139">
-        <v>-4.54</v>
+        <v>-6.9100000000000001</v>
       </c>
       <c r="E16" s="140">
         <v>0</v>
       </c>
       <c r="F16" s="141">
-        <v>0.14515130000000001</v>
+        <v>0.1145709</v>
       </c>
       <c r="G16" s="142">
-        <v>0.4649857</v>
+        <v>0.29833140000000002</v>
       </c>
     </row>
     <row r="17">
@@ -10624,22 +10624,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="161">
-        <v>0.4613177</v>
+        <v>0.46055570000000001</v>
       </c>
       <c r="C19" s="162">
-        <v>0.034944900000000001</v>
+        <v>0.034884199999999997</v>
       </c>
       <c r="D19" s="163">
-        <v>-10.210000000000001</v>
+        <v>-10.24</v>
       </c>
       <c r="E19" s="164">
         <v>0</v>
       </c>
       <c r="F19" s="165">
-        <v>0.39766879999999999</v>
+        <v>0.39701700000000001</v>
       </c>
       <c r="G19" s="166">
-        <v>0.53515400000000002</v>
+        <v>0.53426320000000005</v>
       </c>
     </row>
     <row r="20">
@@ -10647,22 +10647,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="169">
-        <v>1.709908</v>
+        <v>1.211406</v>
       </c>
       <c r="C20" s="170">
-        <v>0.3356365</v>
+        <v>0.1187851</v>
       </c>
       <c r="D20" s="171">
-        <v>2.73</v>
+        <v>1.96</v>
       </c>
       <c r="E20" s="172">
-        <v>0.0060000000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F20" s="173">
-        <v>1.163834</v>
+        <v>0.99959640000000005</v>
       </c>
       <c r="G20" s="174">
-        <v>2.5122019999999998</v>
+        <v>1.468097</v>
       </c>
     </row>
     <row r="21">
@@ -10670,22 +10670,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="177">
-        <v>0.4054622</v>
+        <v>0.28581230000000002</v>
       </c>
       <c r="C21" s="178">
-        <v>0.074797000000000002</v>
+        <v>0.019691799999999999</v>
       </c>
       <c r="D21" s="179">
-        <v>-4.8899999999999997</v>
+        <v>-18.18</v>
       </c>
       <c r="E21" s="180">
         <v>0</v>
       </c>
       <c r="F21" s="181">
-        <v>0.28244010000000003</v>
+        <v>0.2497095</v>
       </c>
       <c r="G21" s="182">
-        <v>0.58206910000000001</v>
+        <v>0.3271348</v>
       </c>
     </row>
     <row r="22">
@@ -10739,22 +10739,22 @@
         <v>18</v>
       </c>
       <c r="B24" s="201">
-        <v>0.55556879999999997</v>
+        <v>0.55407949999999995</v>
       </c>
       <c r="C24" s="202">
-        <v>0.1522713</v>
+        <v>0.15184890000000001</v>
       </c>
       <c r="D24" s="203">
-        <v>-2.1400000000000001</v>
+        <v>-2.1499999999999999</v>
       </c>
       <c r="E24" s="204">
-        <v>0.032000000000000001</v>
+        <v>0.031</v>
       </c>
       <c r="F24" s="205">
-        <v>0.3246677</v>
+        <v>0.32381359999999998</v>
       </c>
       <c r="G24" s="206">
-        <v>0.950685</v>
+        <v>0.94808890000000001</v>
       </c>
     </row>
     <row r="25">
@@ -10762,22 +10762,22 @@
         <v>19</v>
       </c>
       <c r="B25" s="209">
-        <v>1.236496</v>
+        <v>0.87248729999999997</v>
       </c>
       <c r="C25" s="210">
-        <v>0.30013430000000002</v>
+        <v>0.15149499999999999</v>
       </c>
       <c r="D25" s="211">
-        <v>0.87</v>
+        <v>-0.79000000000000004</v>
       </c>
       <c r="E25" s="212">
-        <v>0.38200000000000001</v>
+        <v>0.432</v>
       </c>
       <c r="F25" s="213">
-        <v>0.76838810000000002</v>
+        <v>0.62081200000000003</v>
       </c>
       <c r="G25" s="214">
-        <v>1.9897769999999999</v>
+        <v>1.226191</v>
       </c>
     </row>
     <row r="26">
@@ -10785,22 +10785,22 @@
         <v>20</v>
       </c>
       <c r="B26" s="217">
-        <v>0.53445279999999995</v>
+        <v>0.38366410000000001</v>
       </c>
       <c r="C26" s="218">
-        <v>0.1794161</v>
+        <v>0.1128522</v>
       </c>
       <c r="D26" s="219">
-        <v>-1.8700000000000001</v>
+        <v>-3.2599999999999998</v>
       </c>
       <c r="E26" s="220">
-        <v>0.062</v>
+        <v>0.001</v>
       </c>
       <c r="F26" s="221">
-        <v>0.2767965</v>
+        <v>0.2155639</v>
       </c>
       <c r="G26" s="222">
-        <v>1.031949</v>
+        <v>0.68285169999999995</v>
       </c>
     </row>
     <row r="27">
@@ -10831,22 +10831,22 @@
         <v>23</v>
       </c>
       <c r="B28" s="233">
-        <v>0.62077890000000002</v>
+        <v>0.61854469999999995</v>
       </c>
       <c r="C28" s="234">
-        <v>0.056664800000000001</v>
+        <v>0.056505</v>
       </c>
       <c r="D28" s="235">
-        <v>-5.2199999999999998</v>
+        <v>-5.2599999999999998</v>
       </c>
       <c r="E28" s="236">
         <v>0</v>
       </c>
       <c r="F28" s="237">
-        <v>0.51908589999999999</v>
+        <v>0.51714530000000003</v>
       </c>
       <c r="G28" s="238">
-        <v>0.74239449999999996</v>
+        <v>0.73982610000000004</v>
       </c>
     </row>
     <row r="29">
@@ -10854,22 +10854,22 @@
         <v>24</v>
       </c>
       <c r="B29" s="241">
-        <v>0.94324410000000003</v>
+        <v>0.94420899999999997</v>
       </c>
       <c r="C29" s="242">
-        <v>0.036986100000000001</v>
+        <v>0.0370184</v>
       </c>
       <c r="D29" s="243">
-        <v>-1.49</v>
+        <v>-1.46</v>
       </c>
       <c r="E29" s="244">
-        <v>0.13600000000000001</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="F29" s="245">
-        <v>0.87346840000000003</v>
+        <v>0.87437180000000003</v>
       </c>
       <c r="G29" s="246">
-        <v>1.018594</v>
+        <v>1.0196240000000001</v>
       </c>
     </row>
     <row r="30">
@@ -10877,22 +10877,22 @@
         <v>25</v>
       </c>
       <c r="B30" s="249">
-        <v>0.37080049999999998</v>
+        <v>0.3706199</v>
       </c>
       <c r="C30" s="250">
-        <v>0.017381299999999999</v>
+        <v>0.017372200000000001</v>
       </c>
       <c r="D30" s="251">
-        <v>-21.16</v>
+        <v>-21.18</v>
       </c>
       <c r="E30" s="252">
         <v>0</v>
       </c>
       <c r="F30" s="253">
-        <v>0.33825179999999999</v>
+        <v>0.33808820000000001</v>
       </c>
       <c r="G30" s="254">
-        <v>0.40648109999999999</v>
+        <v>0.40628180000000003</v>
       </c>
     </row>
     <row r="31">
@@ -10900,22 +10900,22 @@
         <v>26</v>
       </c>
       <c r="B31" s="257">
-        <v>0.61669490000000005</v>
+        <v>0.61722809999999995</v>
       </c>
       <c r="C31" s="258">
-        <v>0.022101699999999999</v>
+        <v>0.0221183</v>
       </c>
       <c r="D31" s="259">
-        <v>-13.49</v>
+        <v>-13.460000000000001</v>
       </c>
       <c r="E31" s="260">
         <v>0</v>
       </c>
       <c r="F31" s="261">
-        <v>0.57486280000000001</v>
+        <v>0.57536430000000005</v>
       </c>
       <c r="G31" s="262">
-        <v>0.66157100000000002</v>
+        <v>0.6621378</v>
       </c>
     </row>
     <row r="32">
@@ -10923,22 +10923,22 @@
         <v>27</v>
       </c>
       <c r="B32" s="265">
-        <v>1.024198</v>
+        <v>1.024848</v>
       </c>
       <c r="C32" s="266">
-        <v>0.038164200000000002</v>
+        <v>0.038185499999999997</v>
       </c>
       <c r="D32" s="267">
-        <v>0.64000000000000001</v>
+        <v>0.66000000000000003</v>
       </c>
       <c r="E32" s="268">
-        <v>0.52100000000000002</v>
+        <v>0.51000000000000001</v>
       </c>
       <c r="F32" s="269">
-        <v>0.95206329999999995</v>
+        <v>0.95267270000000004</v>
       </c>
       <c r="G32" s="270">
-        <v>1.1017969999999999</v>
+        <v>1.10249</v>
       </c>
     </row>
     <row r="33">
@@ -10946,22 +10946,22 @@
         <v>28</v>
       </c>
       <c r="B33" s="273">
-        <v>1.3181700000000001</v>
+        <v>1.3211790000000001</v>
       </c>
       <c r="C33" s="274">
-        <v>0.055775400000000003</v>
+        <v>0.0558938</v>
       </c>
       <c r="D33" s="275">
-        <v>6.5300000000000002</v>
+        <v>6.5800000000000001</v>
       </c>
       <c r="E33" s="276">
         <v>0</v>
       </c>
       <c r="F33" s="277">
-        <v>1.213263</v>
+        <v>1.216048</v>
       </c>
       <c r="G33" s="278">
-        <v>1.4321489999999999</v>
+        <v>1.4353990000000001</v>
       </c>
     </row>
     <row r="34">
@@ -10969,22 +10969,22 @@
         <v>29</v>
       </c>
       <c r="B34" s="281">
-        <v>1.344106</v>
+        <v>1.3510329999999999</v>
       </c>
       <c r="C34" s="282">
-        <v>0.12509809999999999</v>
+        <v>0.12576270000000001</v>
       </c>
       <c r="D34" s="283">
-        <v>3.1800000000000002</v>
+        <v>3.23</v>
       </c>
       <c r="E34" s="284">
         <v>0.001</v>
       </c>
       <c r="F34" s="285">
-        <v>1.119982</v>
+        <v>1.125721</v>
       </c>
       <c r="G34" s="286">
-        <v>1.6130819999999999</v>
+        <v>1.6214409999999999</v>
       </c>
     </row>
     <row r="35">
@@ -10992,22 +10992,22 @@
         <v>30</v>
       </c>
       <c r="B35" s="289">
-        <v>0.75188670000000002</v>
+        <v>0.75261800000000001</v>
       </c>
       <c r="C35" s="290">
-        <v>0.046022399999999998</v>
+        <v>0.046063100000000003</v>
       </c>
       <c r="D35" s="291">
-        <v>-4.6600000000000001</v>
+        <v>-4.6399999999999997</v>
       </c>
       <c r="E35" s="292">
         <v>0</v>
       </c>
       <c r="F35" s="293">
-        <v>0.66688499999999995</v>
+        <v>0.66754080000000005</v>
       </c>
       <c r="G35" s="294">
-        <v>0.84772270000000005</v>
+        <v>0.84853809999999996</v>
       </c>
     </row>
     <row r="36">
@@ -11015,10 +11015,10 @@
         <v>31</v>
       </c>
       <c r="B36" s="297">
-        <v>0.66949479999999995</v>
+        <v>0.6694888</v>
       </c>
       <c r="C36" s="298">
-        <v>0.038837400000000001</v>
+        <v>0.038833800000000002</v>
       </c>
       <c r="D36" s="299">
         <v>-6.9199999999999999</v>
@@ -11027,10 +11027,10 @@
         <v>0</v>
       </c>
       <c r="F36" s="301">
-        <v>0.59754269999999998</v>
+        <v>0.59754300000000005</v>
       </c>
       <c r="G36" s="302">
-        <v>0.75011079999999997</v>
+        <v>0.75009700000000001</v>
       </c>
     </row>
     <row r="37">
@@ -11038,22 +11038,22 @@
         <v>32</v>
       </c>
       <c r="B37" s="305">
-        <v>0.5705228</v>
+        <v>0.57534320000000006</v>
       </c>
       <c r="C37" s="306">
-        <v>0.035507499999999997</v>
+        <v>0.0357233</v>
       </c>
       <c r="D37" s="307">
-        <v>-9.0199999999999996</v>
+        <v>-8.9000000000000004</v>
       </c>
       <c r="E37" s="308">
         <v>0</v>
       </c>
       <c r="F37" s="309">
-        <v>0.50500639999999997</v>
+        <v>0.50941939999999997</v>
       </c>
       <c r="G37" s="310">
-        <v>0.64453870000000002</v>
+        <v>0.64979819999999999</v>
       </c>
     </row>
     <row r="38">
@@ -11061,22 +11061,22 @@
         <v>33</v>
       </c>
       <c r="B38" s="313">
-        <v>0.78287119999999999</v>
+        <v>0.7823618</v>
       </c>
       <c r="C38" s="314">
-        <v>0.058809100000000003</v>
+        <v>0.058772600000000001</v>
       </c>
       <c r="D38" s="315">
-        <v>-3.2599999999999998</v>
+        <v>-3.27</v>
       </c>
       <c r="E38" s="316">
         <v>0.001</v>
       </c>
       <c r="F38" s="317">
-        <v>0.67569120000000005</v>
+        <v>0.67524850000000003</v>
       </c>
       <c r="G38" s="318">
-        <v>0.90705239999999998</v>
+        <v>0.90646629999999995</v>
       </c>
     </row>
     <row r="39">
@@ -11084,22 +11084,22 @@
         <v>34</v>
       </c>
       <c r="B39" s="321">
-        <v>1.001849</v>
+        <v>1.0010699999999999</v>
       </c>
       <c r="C39" s="322">
-        <v>0.0065202999999999997</v>
+        <v>0.0065053999999999997</v>
       </c>
       <c r="D39" s="323">
-        <v>0.28000000000000003</v>
+        <v>0.16</v>
       </c>
       <c r="E39" s="324">
-        <v>0.77700000000000002</v>
+        <v>0.869</v>
       </c>
       <c r="F39" s="325">
-        <v>0.98915030000000004</v>
+        <v>0.98840059999999996</v>
       </c>
       <c r="G39" s="326">
-        <v>1.01471</v>
+        <v>1.0139020000000001</v>
       </c>
     </row>
     <row r="40">
@@ -11107,22 +11107,22 @@
         <v>35</v>
       </c>
       <c r="B40" s="329">
-        <v>0.9206953</v>
+        <v>0.91992850000000004</v>
       </c>
       <c r="C40" s="330">
-        <v>0.084301000000000001</v>
+        <v>0.0842194</v>
       </c>
       <c r="D40" s="331">
-        <v>-0.90000000000000002</v>
+        <v>-0.91000000000000003</v>
       </c>
       <c r="E40" s="332">
-        <v>0.36699999999999999</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="F40" s="333">
-        <v>0.76944570000000001</v>
+        <v>0.76882349999999999</v>
       </c>
       <c r="G40" s="334">
-        <v>1.1016760000000001</v>
+        <v>1.100732</v>
       </c>
     </row>
     <row r="41">
@@ -11130,22 +11130,22 @@
         <v>36</v>
       </c>
       <c r="B41" s="337">
-        <v>0.74381160000000002</v>
+        <v>0.74411839999999996</v>
       </c>
       <c r="C41" s="338">
-        <v>0.032690400000000001</v>
+        <v>0.032703299999999998</v>
       </c>
       <c r="D41" s="339">
-        <v>-6.7300000000000004</v>
+        <v>-6.7199999999999998</v>
       </c>
       <c r="E41" s="340">
         <v>0</v>
       </c>
       <c r="F41" s="341">
-        <v>0.68242170000000002</v>
+        <v>0.68270419999999998</v>
       </c>
       <c r="G41" s="342">
-        <v>0.81072409999999995</v>
+        <v>0.81105729999999998</v>
       </c>
     </row>
     <row r="42">
@@ -11153,22 +11153,22 @@
         <v>37</v>
       </c>
       <c r="B42" s="345">
-        <v>0.58080270000000001</v>
+        <v>0.58266620000000002</v>
       </c>
       <c r="C42" s="346">
-        <v>0.0554826</v>
+        <v>0.055627000000000003</v>
       </c>
       <c r="D42" s="347">
-        <v>-5.6900000000000004</v>
+        <v>-5.6600000000000001</v>
       </c>
       <c r="E42" s="348">
         <v>0</v>
       </c>
       <c r="F42" s="349">
-        <v>0.48163230000000001</v>
+        <v>0.4832321</v>
       </c>
       <c r="G42" s="350">
-        <v>0.70039289999999999</v>
+        <v>0.70256070000000004</v>
       </c>
     </row>
     <row r="43">
@@ -11176,22 +11176,22 @@
         <v>38</v>
       </c>
       <c r="B43" s="353">
-        <v>0.66202450000000002</v>
+        <v>0.66170439999999997</v>
       </c>
       <c r="C43" s="354">
-        <v>0.039021899999999998</v>
+        <v>0.039001500000000001</v>
       </c>
       <c r="D43" s="355">
-        <v>-7</v>
+        <v>-7.0099999999999998</v>
       </c>
       <c r="E43" s="356">
         <v>0</v>
       </c>
       <c r="F43" s="357">
-        <v>0.58979539999999997</v>
+        <v>0.58951310000000001</v>
       </c>
       <c r="G43" s="358">
-        <v>0.74309910000000001</v>
+        <v>0.74273630000000002</v>
       </c>
     </row>
     <row r="44">
@@ -11199,10 +11199,10 @@
         <v>39</v>
       </c>
       <c r="B44" s="361">
-        <v>0.65536640000000002</v>
+        <v>0.65550010000000003</v>
       </c>
       <c r="C44" s="362">
-        <v>0.037515899999999998</v>
+        <v>0.037522699999999999</v>
       </c>
       <c r="D44" s="363">
         <v>-7.3799999999999999</v>
@@ -11211,10 +11211,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="365">
-        <v>0.58581139999999998</v>
+        <v>0.58593249999999997</v>
       </c>
       <c r="G44" s="366">
-        <v>0.73317980000000005</v>
+        <v>0.73332739999999996</v>
       </c>
     </row>
     <row r="45">
@@ -11222,22 +11222,22 @@
         <v>40</v>
       </c>
       <c r="B45" s="369">
-        <v>0.51136119999999996</v>
+        <v>0.51033649999999997</v>
       </c>
       <c r="C45" s="370">
-        <v>0.19894770000000001</v>
+        <v>0.1985391</v>
       </c>
       <c r="D45" s="371">
-        <v>-1.72</v>
+        <v>-1.73</v>
       </c>
       <c r="E45" s="372">
-        <v>0.085000000000000006</v>
+        <v>0.084000000000000005</v>
       </c>
       <c r="F45" s="373">
-        <v>0.23854120000000001</v>
+        <v>0.23807229999999999</v>
       </c>
       <c r="G45" s="374">
-        <v>1.096206</v>
+        <v>1.0939669999999999</v>
       </c>
     </row>
     <row r="46">
@@ -11245,22 +11245,22 @@
         <v>41</v>
       </c>
       <c r="B46" s="377">
-        <v>1.2574799999999999</v>
+        <v>1.258014</v>
       </c>
       <c r="C46" s="378">
-        <v>0.031416199999999998</v>
+        <v>0.0314293</v>
       </c>
       <c r="D46" s="379">
-        <v>9.1699999999999999</v>
+        <v>9.1899999999999995</v>
       </c>
       <c r="E46" s="380">
         <v>0</v>
       </c>
       <c r="F46" s="381">
-        <v>1.1973879999999999</v>
+        <v>1.1978979999999999</v>
       </c>
       <c r="G46" s="382">
-        <v>1.320587</v>
+        <v>1.321148</v>
       </c>
     </row>
     <row r="47">
@@ -11268,22 +11268,22 @@
         <v>42</v>
       </c>
       <c r="B47" s="385">
-        <v>0.8840266</v>
+        <v>0.88331879999999996</v>
       </c>
       <c r="C47" s="386">
-        <v>0.013392899999999999</v>
+        <v>0.0133797</v>
       </c>
       <c r="D47" s="387">
-        <v>-8.1400000000000006</v>
+        <v>-8.1899999999999995</v>
       </c>
       <c r="E47" s="388">
         <v>0</v>
       </c>
       <c r="F47" s="389">
-        <v>0.8581628</v>
+        <v>0.85748060000000004</v>
       </c>
       <c r="G47" s="390">
-        <v>0.91066979999999997</v>
+        <v>0.90993559999999996</v>
       </c>
     </row>
     <row r="48">
@@ -11291,10 +11291,10 @@
         <v>43</v>
       </c>
       <c r="B48" s="393">
-        <v>0.77310480000000004</v>
+        <v>0.77317499999999995</v>
       </c>
       <c r="C48" s="394">
-        <v>0.029943899999999999</v>
+        <v>0.029949400000000001</v>
       </c>
       <c r="D48" s="395">
         <v>-6.6399999999999997</v>
@@ -11303,10 +11303,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="397">
-        <v>0.71658820000000001</v>
+        <v>0.71664810000000001</v>
       </c>
       <c r="G48" s="398">
-        <v>0.83407889999999996</v>
+        <v>0.83416049999999997</v>
       </c>
     </row>
     <row r="49">
@@ -11314,22 +11314,22 @@
         <v>44</v>
       </c>
       <c r="B49" s="401">
-        <v>0.82659609999999995</v>
+        <v>0.8259282</v>
       </c>
       <c r="C49" s="402">
-        <v>0.044977900000000001</v>
+        <v>0.044939100000000003</v>
       </c>
       <c r="D49" s="403">
-        <v>-3.5</v>
+        <v>-3.5099999999999998</v>
       </c>
       <c r="E49" s="404">
         <v>0</v>
       </c>
       <c r="F49" s="405">
-        <v>0.74297919999999995</v>
+        <v>0.74238309999999996</v>
       </c>
       <c r="G49" s="406">
-        <v>0.91962350000000004</v>
+        <v>0.9188752</v>
       </c>
     </row>
     <row r="50">
@@ -11337,22 +11337,22 @@
         <v>45</v>
       </c>
       <c r="B50" s="409">
-        <v>0.72591669999999997</v>
+        <v>0.72623340000000003</v>
       </c>
       <c r="C50" s="410">
-        <v>0.019868400000000001</v>
+        <v>0.019874699999999999</v>
       </c>
       <c r="D50" s="411">
-        <v>-11.699999999999999</v>
+        <v>-11.69</v>
       </c>
       <c r="E50" s="412">
         <v>0</v>
       </c>
       <c r="F50" s="413">
-        <v>0.68800130000000004</v>
+        <v>0.68830590000000003</v>
       </c>
       <c r="G50" s="414">
-        <v>0.76592150000000003</v>
+        <v>0.76625069999999995</v>
       </c>
     </row>
     <row r="51">
@@ -11360,10 +11360,10 @@
         <v>46</v>
       </c>
       <c r="B51" s="417">
-        <v>1.0912660000000001</v>
+        <v>1.091251</v>
       </c>
       <c r="C51" s="418">
-        <v>0.074395199999999995</v>
+        <v>0.074403399999999995</v>
       </c>
       <c r="D51" s="419">
         <v>1.28</v>
@@ -11372,10 +11372,10 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="F51" s="421">
-        <v>0.95477599999999996</v>
+        <v>0.95474680000000001</v>
       </c>
       <c r="G51" s="422">
-        <v>1.247268</v>
+        <v>1.2472719999999999</v>
       </c>
     </row>
     <row r="52">
@@ -11383,22 +11383,22 @@
         <v>47</v>
       </c>
       <c r="B52" s="425">
-        <v>0.8106778</v>
+        <v>0.80988649999999995</v>
       </c>
       <c r="C52" s="426">
-        <v>0.043542200000000003</v>
+        <v>0.043495800000000001</v>
       </c>
       <c r="D52" s="427">
-        <v>-3.9100000000000001</v>
+        <v>-3.9300000000000002</v>
       </c>
       <c r="E52" s="428">
         <v>0</v>
       </c>
       <c r="F52" s="429">
-        <v>0.72967499999999996</v>
+        <v>0.7289696</v>
       </c>
       <c r="G52" s="430">
-        <v>0.9006729</v>
+        <v>0.89978519999999995</v>
       </c>
     </row>
     <row r="53">
@@ -11406,22 +11406,22 @@
         <v>48</v>
       </c>
       <c r="B53" s="433">
-        <v>0.9698909</v>
+        <v>0.97011939999999997</v>
       </c>
       <c r="C53" s="434">
-        <v>0.0249172</v>
+        <v>0.024922099999999999</v>
       </c>
       <c r="D53" s="435">
-        <v>-1.19</v>
+        <v>-1.1799999999999999</v>
       </c>
       <c r="E53" s="436">
-        <v>0.23400000000000001</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="F53" s="437">
-        <v>0.92226319999999995</v>
+        <v>0.92248240000000004</v>
       </c>
       <c r="G53" s="438">
-        <v>1.0199780000000001</v>
+        <v>1.020216</v>
       </c>
     </row>
     <row r="54">
@@ -11429,22 +11429,22 @@
         <v>49</v>
       </c>
       <c r="B54" s="441">
-        <v>0.83589780000000002</v>
+        <v>0.8355688</v>
       </c>
       <c r="C54" s="442">
-        <v>0.0226243</v>
+        <v>0.0226137</v>
       </c>
       <c r="D54" s="443">
-        <v>-6.6200000000000001</v>
+        <v>-6.6399999999999997</v>
       </c>
       <c r="E54" s="444">
         <v>0</v>
       </c>
       <c r="F54" s="445">
-        <v>0.79271069999999999</v>
+        <v>0.79240180000000005</v>
       </c>
       <c r="G54" s="446">
-        <v>0.88143780000000005</v>
+        <v>0.88108739999999997</v>
       </c>
     </row>
     <row r="55">
@@ -11475,22 +11475,22 @@
         <v>52</v>
       </c>
       <c r="B56" s="457">
-        <v>0.7216747</v>
+        <v>0.7207346</v>
       </c>
       <c r="C56" s="458">
-        <v>0.068934200000000001</v>
+        <v>0.068832000000000004</v>
       </c>
       <c r="D56" s="459">
-        <v>-3.4100000000000001</v>
+        <v>-3.4300000000000002</v>
       </c>
       <c r="E56" s="460">
         <v>0.001</v>
       </c>
       <c r="F56" s="461">
-        <v>0.59845970000000004</v>
+        <v>0.59770029999999996</v>
       </c>
       <c r="G56" s="462">
-        <v>0.87025790000000003</v>
+        <v>0.86909510000000001</v>
       </c>
     </row>
     <row r="57">
@@ -11498,22 +11498,22 @@
         <v>53</v>
       </c>
       <c r="B57" s="465">
-        <v>0.80537550000000002</v>
+        <v>0.80580439999999998</v>
       </c>
       <c r="C57" s="466">
-        <v>0.081134200000000004</v>
+        <v>0.081165200000000007</v>
       </c>
       <c r="D57" s="467">
-        <v>-2.1499999999999999</v>
+        <v>-2.1400000000000001</v>
       </c>
       <c r="E57" s="468">
         <v>0.032000000000000001</v>
       </c>
       <c r="F57" s="469">
-        <v>0.66107020000000005</v>
+        <v>0.66144199999999998</v>
       </c>
       <c r="G57" s="470">
-        <v>0.98118110000000003</v>
+        <v>0.98167439999999995</v>
       </c>
     </row>
     <row r="58">
@@ -11521,22 +11521,22 @@
         <v>54</v>
       </c>
       <c r="B58" s="473">
-        <v>0.77167459999999999</v>
+        <v>0.77043819999999996</v>
       </c>
       <c r="C58" s="474">
-        <v>0.067846299999999998</v>
+        <v>0.067723800000000001</v>
       </c>
       <c r="D58" s="475">
-        <v>-2.9500000000000002</v>
+        <v>-2.9700000000000002</v>
       </c>
       <c r="E58" s="476">
         <v>0.0030000000000000001</v>
       </c>
       <c r="F58" s="477">
-        <v>0.64952489999999996</v>
+        <v>0.64850699999999995</v>
       </c>
       <c r="G58" s="478">
-        <v>0.91679580000000005</v>
+        <v>0.91529459999999996</v>
       </c>
     </row>
     <row r="59">
@@ -11544,22 +11544,22 @@
         <v>55</v>
       </c>
       <c r="B59" s="481">
-        <v>1.4178489999999999</v>
+        <v>1.4161280000000001</v>
       </c>
       <c r="C59" s="482">
-        <v>0.1211749</v>
+        <v>0.1210027</v>
       </c>
       <c r="D59" s="483">
-        <v>4.0899999999999999</v>
+        <v>4.0700000000000003</v>
       </c>
       <c r="E59" s="484">
         <v>0</v>
       </c>
       <c r="F59" s="485">
-        <v>1.199176</v>
+        <v>1.1977629999999999</v>
       </c>
       <c r="G59" s="486">
-        <v>1.6763969999999999</v>
+        <v>1.6743049999999999</v>
       </c>
     </row>
     <row r="60">
@@ -11567,22 +11567,22 @@
         <v>56</v>
       </c>
       <c r="B60" s="489">
-        <v>1.762564</v>
+        <v>1.7580359999999999</v>
       </c>
       <c r="C60" s="490">
-        <v>1.7799590000000001</v>
+        <v>1.7752589999999999</v>
       </c>
       <c r="D60" s="491">
         <v>0.56000000000000005</v>
       </c>
       <c r="E60" s="492">
-        <v>0.57499999999999996</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="F60" s="493">
-        <v>0.24352470000000001</v>
+        <v>0.2429337</v>
       </c>
       <c r="G60" s="494">
-        <v>12.75695</v>
+        <v>12.72237</v>
       </c>
     </row>
     <row r="61">
@@ -11590,22 +11590,22 @@
         <v>57</v>
       </c>
       <c r="B61" s="497">
-        <v>0.75496629999999998</v>
+        <v>0.75599850000000002</v>
       </c>
       <c r="C61" s="498">
-        <v>0.0324512</v>
+        <v>0.032480200000000001</v>
       </c>
       <c r="D61" s="499">
-        <v>-6.54</v>
+        <v>-6.5099999999999998</v>
       </c>
       <c r="E61" s="500">
         <v>0</v>
       </c>
       <c r="F61" s="501">
-        <v>0.69396849999999999</v>
+        <v>0.69494500000000003</v>
       </c>
       <c r="G61" s="502">
-        <v>0.82132559999999999</v>
+        <v>0.82241569999999997</v>
       </c>
     </row>
     <row r="62">
@@ -11613,22 +11613,22 @@
         <v>58</v>
       </c>
       <c r="B62" s="505">
-        <v>0.8953122</v>
+        <v>0.89424119999999996</v>
       </c>
       <c r="C62" s="506">
-        <v>0.0410359</v>
+        <v>0.040978000000000001</v>
       </c>
       <c r="D62" s="507">
-        <v>-2.4100000000000001</v>
+        <v>-2.44</v>
       </c>
       <c r="E62" s="508">
-        <v>0.016</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="F62" s="509">
-        <v>0.81839010000000001</v>
+        <v>0.81742680000000001</v>
       </c>
       <c r="G62" s="510">
-        <v>0.97946429999999996</v>
+        <v>0.97827379999999997</v>
       </c>
     </row>
     <row r="63">
@@ -11636,22 +11636,22 @@
         <v>59</v>
       </c>
       <c r="B63" s="513">
-        <v>1.0554969999999999</v>
+        <v>1.056961</v>
       </c>
       <c r="C63" s="514">
-        <v>0.039192900000000003</v>
+        <v>0.039246200000000002</v>
       </c>
       <c r="D63" s="515">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="E63" s="516">
-        <v>0.14599999999999999</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="F63" s="517">
-        <v>0.98140870000000002</v>
+        <v>0.98277230000000004</v>
       </c>
       <c r="G63" s="518">
-        <v>1.135178</v>
+        <v>1.1367499999999999</v>
       </c>
     </row>
     <row r="64">
@@ -11659,22 +11659,22 @@
         <v>60</v>
       </c>
       <c r="B64" s="521">
-        <v>1.4941279999999999</v>
+        <v>1.493479</v>
       </c>
       <c r="C64" s="522">
-        <v>0.1229504</v>
+        <v>0.1229049</v>
       </c>
       <c r="D64" s="523">
-        <v>4.8799999999999999</v>
+        <v>4.8700000000000001</v>
       </c>
       <c r="E64" s="524">
         <v>0</v>
       </c>
       <c r="F64" s="525">
-        <v>1.271579</v>
+        <v>1.271013</v>
       </c>
       <c r="G64" s="526">
-        <v>1.755628</v>
+        <v>1.754883</v>
       </c>
     </row>
     <row r="65">
@@ -11682,22 +11682,22 @@
         <v>61</v>
       </c>
       <c r="B65" s="529">
-        <v>1.152841</v>
+        <v>1.1506179999999999</v>
       </c>
       <c r="C65" s="530">
-        <v>0.15695619999999999</v>
+        <v>0.15660560000000001</v>
       </c>
       <c r="D65" s="531">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="E65" s="532">
-        <v>0.29599999999999999</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="F65" s="533">
-        <v>0.88283719999999999</v>
+        <v>0.88120679999999996</v>
       </c>
       <c r="G65" s="534">
-        <v>1.505422</v>
+        <v>1.5023960000000001</v>
       </c>
     </row>
     <row r="66">
@@ -11705,22 +11705,22 @@
         <v>62</v>
       </c>
       <c r="B66" s="537">
-        <v>1.4327350000000001</v>
+        <v>1.4314180000000001</v>
       </c>
       <c r="C66" s="538">
-        <v>1.9158919999999999</v>
+        <v>1.915135</v>
       </c>
       <c r="D66" s="539">
         <v>0.27000000000000002</v>
       </c>
       <c r="E66" s="540">
-        <v>0.78800000000000003</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="F66" s="541">
-        <v>0.1042115</v>
+        <v>0.1039727</v>
       </c>
       <c r="G66" s="542">
-        <v>19.69772</v>
+        <v>19.706679999999999</v>
       </c>
     </row>
     <row r="67">
@@ -11728,22 +11728,22 @@
         <v>63</v>
       </c>
       <c r="B67" s="545">
-        <v>1.036303</v>
+        <v>1.036089</v>
       </c>
       <c r="C67" s="546">
-        <v>0.062786999999999996</v>
+        <v>0.062768900000000002</v>
       </c>
       <c r="D67" s="547">
         <v>0.58999999999999997</v>
       </c>
       <c r="E67" s="548">
-        <v>0.55600000000000005</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="F67" s="549">
-        <v>0.92026859999999999</v>
+        <v>0.92008699999999999</v>
       </c>
       <c r="G67" s="550">
-        <v>1.166968</v>
+        <v>1.166715</v>
       </c>
     </row>
     <row r="68">
@@ -11751,22 +11751,22 @@
         <v>64</v>
       </c>
       <c r="B68" s="553">
-        <v>1.382368</v>
+        <v>1.38398</v>
       </c>
       <c r="C68" s="554">
-        <v>0.085228999999999999</v>
+        <v>0.085350099999999998</v>
       </c>
       <c r="D68" s="555">
-        <v>5.25</v>
+        <v>5.2699999999999996</v>
       </c>
       <c r="E68" s="556">
         <v>0</v>
       </c>
       <c r="F68" s="557">
-        <v>1.22502</v>
+        <v>1.2264120000000001</v>
       </c>
       <c r="G68" s="558">
-        <v>1.5599259999999999</v>
+        <v>1.561793</v>
       </c>
     </row>
     <row r="69">
@@ -11774,22 +11774,22 @@
         <v>65</v>
       </c>
       <c r="B69" s="561">
-        <v>0.93274429999999997</v>
+        <v>0.93648100000000001</v>
       </c>
       <c r="C69" s="562">
-        <v>0.076957700000000004</v>
+        <v>0.0772785</v>
       </c>
       <c r="D69" s="563">
-        <v>-0.83999999999999997</v>
+        <v>-0.80000000000000004</v>
       </c>
       <c r="E69" s="564">
-        <v>0.39900000000000002</v>
+        <v>0.42599999999999999</v>
       </c>
       <c r="F69" s="565">
-        <v>0.79347400000000001</v>
+        <v>0.79663200000000001</v>
       </c>
       <c r="G69" s="566">
-        <v>1.0964590000000001</v>
+        <v>1.100881</v>
       </c>
     </row>
     <row r="70">
@@ -11797,22 +11797,22 @@
         <v>66</v>
       </c>
       <c r="B70" s="569">
-        <v>0.24351680000000001</v>
+        <v>0.24283179999999999</v>
       </c>
       <c r="C70" s="570">
-        <v>0.1397899</v>
+        <v>0.1393258</v>
       </c>
       <c r="D70" s="571">
-        <v>-2.46</v>
+        <v>-2.4700000000000002</v>
       </c>
       <c r="E70" s="572">
         <v>0.014</v>
       </c>
       <c r="F70" s="573">
-        <v>0.079049599999999998</v>
+        <v>0.078872399999999995</v>
       </c>
       <c r="G70" s="574">
-        <v>0.75016700000000003</v>
+        <v>0.74762910000000005</v>
       </c>
     </row>
     <row r="71">
@@ -11820,10 +11820,10 @@
         <v>67</v>
       </c>
       <c r="B71" s="577">
-        <v>1.5965020000000001</v>
+        <v>1.5988100000000001</v>
       </c>
       <c r="C71" s="578">
-        <v>0.21008199999999999</v>
+        <v>0.21047370000000001</v>
       </c>
       <c r="D71" s="579">
         <v>3.5600000000000001</v>
@@ -11832,10 +11832,10 @@
         <v>0</v>
       </c>
       <c r="F71" s="581">
-        <v>1.2335609999999999</v>
+        <v>1.2352110000000001</v>
       </c>
       <c r="G71" s="582">
-        <v>2.066227</v>
+        <v>2.0694379999999999</v>
       </c>
     </row>
     <row r="72">
@@ -11843,22 +11843,22 @@
         <v>68</v>
       </c>
       <c r="B72" s="585">
-        <v>1.219797</v>
+        <v>1.217894</v>
       </c>
       <c r="C72" s="586">
-        <v>0.19766149999999999</v>
+        <v>0.19734779999999999</v>
       </c>
       <c r="D72" s="587">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="E72" s="588">
-        <v>0.22</v>
+        <v>0.224</v>
       </c>
       <c r="F72" s="589">
-        <v>0.88788120000000004</v>
+        <v>0.88650359999999995</v>
       </c>
       <c r="G72" s="590">
-        <v>1.675792</v>
+        <v>1.673163</v>
       </c>
     </row>
     <row r="73">
@@ -11866,22 +11866,22 @@
         <v>69</v>
       </c>
       <c r="B73" s="593">
-        <v>0.85960919999999996</v>
+        <v>0.85905169999999997</v>
       </c>
       <c r="C73" s="594">
-        <v>0.070324899999999996</v>
+        <v>0.070293099999999997</v>
       </c>
       <c r="D73" s="595">
-        <v>-1.8500000000000001</v>
+        <v>-1.8600000000000001</v>
       </c>
       <c r="E73" s="596">
-        <v>0.064000000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="F73" s="597">
-        <v>0.73225779999999996</v>
+        <v>0.73175979999999996</v>
       </c>
       <c r="G73" s="598">
-        <v>1.009109</v>
+        <v>1.008486</v>
       </c>
     </row>
     <row r="74">
@@ -11889,10 +11889,10 @@
         <v>70</v>
       </c>
       <c r="B74" s="601">
-        <v>1.345596</v>
+        <v>1.34568</v>
       </c>
       <c r="C74" s="602">
-        <v>0.1403732</v>
+        <v>0.1403526</v>
       </c>
       <c r="D74" s="603">
         <v>2.8500000000000001</v>
@@ -11901,10 +11901,10 @@
         <v>0.0040000000000000001</v>
       </c>
       <c r="F74" s="605">
-        <v>1.0967739999999999</v>
+        <v>1.096889</v>
       </c>
       <c r="G74" s="606">
-        <v>1.650868</v>
+        <v>1.650901</v>
       </c>
     </row>
     <row r="75">
@@ -11912,22 +11912,22 @@
         <v>71</v>
       </c>
       <c r="B75" s="609">
-        <v>0.99067079999999996</v>
+        <v>0.98489990000000005</v>
       </c>
       <c r="C75" s="610">
-        <v>0.034451900000000001</v>
+        <v>0.034149600000000002</v>
       </c>
       <c r="D75" s="611">
-        <v>-0.27000000000000002</v>
+        <v>-0.44</v>
       </c>
       <c r="E75" s="612">
-        <v>0.78800000000000003</v>
+        <v>0.66100000000000003</v>
       </c>
       <c r="F75" s="613">
-        <v>0.92539610000000005</v>
+        <v>0.9201916</v>
       </c>
       <c r="G75" s="614">
-        <v>1.0605500000000001</v>
+        <v>1.0541579999999999</v>
       </c>
     </row>
     <row r="76">
@@ -11935,22 +11935,22 @@
         <v>72</v>
       </c>
       <c r="B76" s="617">
-        <v>1.0842270000000001</v>
+        <v>1.0699559999999999</v>
       </c>
       <c r="C76" s="618">
-        <v>0.092086899999999999</v>
+        <v>0.090632500000000005</v>
       </c>
       <c r="D76" s="619">
-        <v>0.94999999999999996</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="E76" s="620">
-        <v>0.34100000000000003</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="F76" s="621">
-        <v>0.91796239999999996</v>
+        <v>0.90628240000000004</v>
       </c>
       <c r="G76" s="622">
-        <v>1.2806059999999999</v>
+        <v>1.26319</v>
       </c>
     </row>
     <row r="77">
@@ -11958,22 +11958,22 @@
         <v>73</v>
       </c>
       <c r="B77" s="625">
-        <v>0.83378140000000001</v>
+        <v>0.83623409999999998</v>
       </c>
       <c r="C77" s="626">
-        <v>0.033652799999999997</v>
+        <v>0.0337463</v>
       </c>
       <c r="D77" s="627">
-        <v>-4.5</v>
+        <v>-4.4299999999999997</v>
       </c>
       <c r="E77" s="628">
         <v>0</v>
       </c>
       <c r="F77" s="629">
-        <v>0.77036450000000001</v>
+        <v>0.77264060000000001</v>
       </c>
       <c r="G77" s="630">
-        <v>0.90241879999999997</v>
+        <v>0.90506180000000003</v>
       </c>
     </row>
     <row r="78">
@@ -11981,22 +11981,22 @@
         <v>74</v>
       </c>
       <c r="B78" s="633">
-        <v>1.3566720000000001</v>
+        <v>1.353286</v>
       </c>
       <c r="C78" s="634">
-        <v>0.1870851</v>
+        <v>0.1866082</v>
       </c>
       <c r="D78" s="635">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="E78" s="636">
-        <v>0.027</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="F78" s="637">
-        <v>1.0353669999999999</v>
+        <v>1.032797</v>
       </c>
       <c r="G78" s="638">
-        <v>1.7776879999999999</v>
+        <v>1.773226</v>
       </c>
     </row>
     <row r="79">
@@ -12004,22 +12004,22 @@
         <v>75</v>
       </c>
       <c r="B79" s="641">
-        <v>0.78661049999999999</v>
+        <v>0.78610849999999999</v>
       </c>
       <c r="C79" s="642">
-        <v>0.027761999999999999</v>
+        <v>0.027741399999999999</v>
       </c>
       <c r="D79" s="643">
-        <v>-6.7999999999999998</v>
+        <v>-6.8200000000000003</v>
       </c>
       <c r="E79" s="644">
         <v>0</v>
       </c>
       <c r="F79" s="645">
-        <v>0.7340373</v>
+        <v>0.73357399999999995</v>
       </c>
       <c r="G79" s="646">
-        <v>0.84294910000000001</v>
+        <v>0.84240510000000002</v>
       </c>
     </row>
     <row r="80">
@@ -12027,22 +12027,22 @@
         <v>76</v>
       </c>
       <c r="B80" s="656">
-        <v>3.0528580000000001</v>
+        <v>4.4541620000000002</v>
       </c>
       <c r="C80" s="657">
-        <v>1.379583</v>
+        <v>1.84239</v>
       </c>
       <c r="D80" s="658">
-        <v>2.4700000000000002</v>
+        <v>3.6099999999999999</v>
       </c>
       <c r="E80" s="659">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="F80" s="660">
-        <v>1.259069</v>
+        <v>1.98007</v>
       </c>
       <c r="G80" s="661">
-        <v>7.4022490000000003</v>
+        <v>10.01962</v>
       </c>
     </row>
   </sheetData>

--- a/mortality_odds_all.xlsx
+++ b/mortality_odds_all.xlsx
@@ -10233,22 +10233,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="25">
-        <v>3.8267310000000001</v>
+        <v>1.4714860000000001</v>
       </c>
       <c r="C2" s="26">
-        <v>4.3730690000000001</v>
+        <v>0.27750019999999997</v>
       </c>
       <c r="D2" s="27">
-        <v>1.1699999999999999</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="E2" s="28">
-        <v>0.23999999999999999</v>
+        <v>0.041000000000000002</v>
       </c>
       <c r="F2" s="29">
-        <v>0.40747529999999999</v>
+        <v>1.0167930000000001</v>
       </c>
       <c r="G2" s="30">
-        <v>35.93806</v>
+        <v>2.1295120000000001</v>
       </c>
     </row>
     <row r="3">
@@ -10256,22 +10256,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="33">
-        <v>0.85448279999999999</v>
+        <v>1.226254</v>
       </c>
       <c r="C3" s="34">
-        <v>0.044570100000000001</v>
+        <v>0.22594320000000001</v>
       </c>
       <c r="D3" s="35">
-        <v>-3.0099999999999998</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E3" s="36">
-        <v>0.0030000000000000001</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="F3" s="37">
-        <v>0.77144400000000002</v>
+        <v>0.85455999999999999</v>
       </c>
       <c r="G3" s="38">
-        <v>0.94646010000000003</v>
+        <v>1.7596179999999999</v>
       </c>
     </row>
     <row r="4">
@@ -10279,22 +10279,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="41">
-        <v>1.4093929999999999</v>
+        <v>2.0235910000000001</v>
       </c>
       <c r="C4" s="42">
-        <v>0.10929759999999999</v>
+        <v>0.3911288</v>
       </c>
       <c r="D4" s="43">
-        <v>4.4299999999999997</v>
+        <v>3.6499999999999999</v>
       </c>
       <c r="E4" s="44">
         <v>0</v>
       </c>
       <c r="F4" s="45">
-        <v>1.2106589999999999</v>
+        <v>1.385475</v>
       </c>
       <c r="G4" s="46">
-        <v>1.640749</v>
+        <v>2.9556079999999998</v>
       </c>
     </row>
     <row r="5">
@@ -10302,22 +10302,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="49">
-        <v>0.83954700000000004</v>
+        <v>1.1918010000000001</v>
       </c>
       <c r="C5" s="50">
-        <v>0.059070400000000002</v>
+        <v>0.2200386</v>
       </c>
       <c r="D5" s="51">
-        <v>-2.4900000000000002</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="E5" s="52">
-        <v>0.012999999999999999</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="F5" s="53">
-        <v>0.73139949999999998</v>
+        <v>0.82994460000000003</v>
       </c>
       <c r="G5" s="54">
-        <v>0.96368569999999998</v>
+        <v>1.711428</v>
       </c>
     </row>
     <row r="6">
@@ -10325,22 +10325,22 @@
         <v>11</v>
       </c>
       <c r="B6" s="57">
-        <v>0.2195956</v>
+        <v>1.208744</v>
       </c>
       <c r="C6" s="58">
-        <v>0.25078820000000002</v>
+        <v>0.22718530000000001</v>
       </c>
       <c r="D6" s="59">
-        <v>-1.3300000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="E6" s="60">
-        <v>0.184</v>
+        <v>0.313</v>
       </c>
       <c r="F6" s="61">
-        <v>0.023415999999999999</v>
+        <v>0.83627649999999998</v>
       </c>
       <c r="G6" s="62">
-        <v>2.0593710000000001</v>
+        <v>1.7471049999999999</v>
       </c>
     </row>
     <row r="7">
@@ -10348,22 +10348,22 @@
         <v>12</v>
       </c>
       <c r="B7" s="65">
-        <v>0.90177779999999996</v>
+        <v>1.242551</v>
       </c>
       <c r="C7" s="66">
-        <v>0.26817350000000001</v>
+        <v>0.4269772</v>
       </c>
       <c r="D7" s="67">
-        <v>-0.34999999999999998</v>
+        <v>0.63</v>
       </c>
       <c r="E7" s="68">
-        <v>0.72799999999999998</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="F7" s="69">
-        <v>0.50346190000000002</v>
+        <v>0.63360190000000005</v>
       </c>
       <c r="G7" s="70">
-        <v>1.6152230000000001</v>
+        <v>2.4367570000000001</v>
       </c>
     </row>
     <row r="8">
@@ -10371,22 +10371,22 @@
         <v>13</v>
       </c>
       <c r="B8" s="73">
-        <v>0.67965509999999996</v>
+        <v>0.84171430000000003</v>
       </c>
       <c r="C8" s="74">
-        <v>0.52324990000000005</v>
+        <v>0.66602050000000002</v>
       </c>
       <c r="D8" s="75">
-        <v>-0.5</v>
+        <v>-0.22</v>
       </c>
       <c r="E8" s="76">
-        <v>0.61599999999999999</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="F8" s="77">
-        <v>0.15030350000000001</v>
+        <v>0.17849960000000001</v>
       </c>
       <c r="G8" s="78">
-        <v>3.073321</v>
+        <v>3.9691010000000002</v>
       </c>
     </row>
     <row r="9">
@@ -10394,22 +10394,22 @@
         <v>14</v>
       </c>
       <c r="B9" s="81">
-        <v>0.21361069999999999</v>
+        <v>0.31065199999999998</v>
       </c>
       <c r="C9" s="82">
-        <v>0.2276011</v>
+        <v>0.33587640000000002</v>
       </c>
       <c r="D9" s="83">
-        <v>-1.45</v>
+        <v>-1.0800000000000001</v>
       </c>
       <c r="E9" s="84">
-        <v>0.14699999999999999</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F9" s="85">
-        <v>0.026464999999999999</v>
+        <v>0.037321300000000002</v>
       </c>
       <c r="G9" s="86">
-        <v>1.724145</v>
+        <v>2.5857809999999999</v>
       </c>
     </row>
     <row r="10">
@@ -10417,22 +10417,22 @@
         <v>15</v>
       </c>
       <c r="B10" s="89">
-        <v>0.5302654</v>
+        <v>0.76205319999999999</v>
       </c>
       <c r="C10" s="90">
-        <v>0.1181931</v>
+        <v>0.21710789999999999</v>
       </c>
       <c r="D10" s="91">
-        <v>-2.8500000000000001</v>
+        <v>-0.94999999999999996</v>
       </c>
       <c r="E10" s="92">
-        <v>0.0040000000000000001</v>
+        <v>0.34000000000000002</v>
       </c>
       <c r="F10" s="93">
-        <v>0.34258260000000001</v>
+        <v>0.43599260000000001</v>
       </c>
       <c r="G10" s="94">
-        <v>0.82076959999999999</v>
+        <v>1.331961</v>
       </c>
     </row>
     <row r="11">
@@ -10440,22 +10440,22 @@
         <v>16</v>
       </c>
       <c r="B11" s="97">
-        <v>0.8067571</v>
+        <v>1.158396</v>
       </c>
       <c r="C11" s="98">
-        <v>0.36643559999999997</v>
+        <v>0.56470209999999999</v>
       </c>
       <c r="D11" s="99">
-        <v>-0.46999999999999997</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="E11" s="100">
-        <v>0.63600000000000001</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="F11" s="101">
-        <v>0.33122279999999998</v>
+        <v>0.44556210000000002</v>
       </c>
       <c r="G11" s="102">
-        <v>1.9650129999999999</v>
+        <v>3.0116610000000001</v>
       </c>
     </row>
     <row r="12">
@@ -10509,22 +10509,22 @@
         <v>18</v>
       </c>
       <c r="B14" s="121">
-        <v>0.44733289999999998</v>
+        <v>0.4470266</v>
       </c>
       <c r="C14" s="122">
-        <v>0.061317200000000002</v>
+        <v>0.061254400000000001</v>
       </c>
       <c r="D14" s="123">
-        <v>-5.8700000000000001</v>
+        <v>-5.8799999999999999</v>
       </c>
       <c r="E14" s="124">
         <v>0</v>
       </c>
       <c r="F14" s="125">
-        <v>0.34194350000000001</v>
+        <v>0.3417404</v>
       </c>
       <c r="G14" s="126">
-        <v>0.58520419999999995</v>
+        <v>0.5847502</v>
       </c>
     </row>
     <row r="15">
@@ -10532,22 +10532,22 @@
         <v>19</v>
       </c>
       <c r="B15" s="129">
-        <v>0.2914735</v>
+        <v>0.40945949999999998</v>
       </c>
       <c r="C15" s="130">
-        <v>0.31455850000000002</v>
+        <v>0.44564229999999999</v>
       </c>
       <c r="D15" s="131">
-        <v>-1.1399999999999999</v>
+        <v>-0.81999999999999995</v>
       </c>
       <c r="E15" s="132">
-        <v>0.253</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="F15" s="133">
-        <v>0.035154499999999998</v>
+        <v>0.0485055</v>
       </c>
       <c r="G15" s="134">
-        <v>2.4166669999999999</v>
+        <v>3.4564539999999999</v>
       </c>
     </row>
     <row r="16">
@@ -10555,22 +10555,22 @@
         <v>20</v>
       </c>
       <c r="B16" s="137">
-        <v>0.1848786</v>
+        <v>0.25979469999999999</v>
       </c>
       <c r="C16" s="138">
-        <v>0.045136200000000001</v>
+        <v>0.077159800000000001</v>
       </c>
       <c r="D16" s="139">
-        <v>-6.9100000000000001</v>
+        <v>-4.54</v>
       </c>
       <c r="E16" s="140">
         <v>0</v>
       </c>
       <c r="F16" s="141">
-        <v>0.1145709</v>
+        <v>0.14515130000000001</v>
       </c>
       <c r="G16" s="142">
-        <v>0.29833140000000002</v>
+        <v>0.4649857</v>
       </c>
     </row>
     <row r="17">
@@ -10624,22 +10624,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="161">
-        <v>0.46055570000000001</v>
+        <v>0.4613177</v>
       </c>
       <c r="C19" s="162">
-        <v>0.034884199999999997</v>
+        <v>0.034944900000000001</v>
       </c>
       <c r="D19" s="163">
-        <v>-10.24</v>
+        <v>-10.210000000000001</v>
       </c>
       <c r="E19" s="164">
         <v>0</v>
       </c>
       <c r="F19" s="165">
-        <v>0.39701700000000001</v>
+        <v>0.39766879999999999</v>
       </c>
       <c r="G19" s="166">
-        <v>0.53426320000000005</v>
+        <v>0.53515400000000002</v>
       </c>
     </row>
     <row r="20">
@@ -10647,22 +10647,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="169">
-        <v>1.211406</v>
+        <v>1.709908</v>
       </c>
       <c r="C20" s="170">
-        <v>0.1187851</v>
+        <v>0.3356365</v>
       </c>
       <c r="D20" s="171">
-        <v>1.96</v>
+        <v>2.73</v>
       </c>
       <c r="E20" s="172">
-        <v>0.050000000000000003</v>
+        <v>0.0060000000000000001</v>
       </c>
       <c r="F20" s="173">
-        <v>0.99959640000000005</v>
+        <v>1.163834</v>
       </c>
       <c r="G20" s="174">
-        <v>1.468097</v>
+        <v>2.5122019999999998</v>
       </c>
     </row>
     <row r="21">
@@ -10670,22 +10670,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="177">
-        <v>0.28581230000000002</v>
+        <v>0.4054622</v>
       </c>
       <c r="C21" s="178">
-        <v>0.019691799999999999</v>
+        <v>0.074797000000000002</v>
       </c>
       <c r="D21" s="179">
-        <v>-18.18</v>
+        <v>-4.8899999999999997</v>
       </c>
       <c r="E21" s="180">
         <v>0</v>
       </c>
       <c r="F21" s="181">
-        <v>0.2497095</v>
+        <v>0.28244010000000003</v>
       </c>
       <c r="G21" s="182">
-        <v>0.3271348</v>
+        <v>0.58206910000000001</v>
       </c>
     </row>
     <row r="22">
@@ -10739,22 +10739,22 @@
         <v>18</v>
       </c>
       <c r="B24" s="201">
-        <v>0.55407949999999995</v>
+        <v>0.55556879999999997</v>
       </c>
       <c r="C24" s="202">
-        <v>0.15184890000000001</v>
+        <v>0.1522713</v>
       </c>
       <c r="D24" s="203">
-        <v>-2.1499999999999999</v>
+        <v>-2.1400000000000001</v>
       </c>
       <c r="E24" s="204">
-        <v>0.031</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="F24" s="205">
-        <v>0.32381359999999998</v>
+        <v>0.3246677</v>
       </c>
       <c r="G24" s="206">
-        <v>0.94808890000000001</v>
+        <v>0.950685</v>
       </c>
     </row>
     <row r="25">
@@ -10762,22 +10762,22 @@
         <v>19</v>
       </c>
       <c r="B25" s="209">
-        <v>0.87248729999999997</v>
+        <v>1.236496</v>
       </c>
       <c r="C25" s="210">
-        <v>0.15149499999999999</v>
+        <v>0.30013430000000002</v>
       </c>
       <c r="D25" s="211">
-        <v>-0.79000000000000004</v>
+        <v>0.87</v>
       </c>
       <c r="E25" s="212">
-        <v>0.432</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="F25" s="213">
-        <v>0.62081200000000003</v>
+        <v>0.76838810000000002</v>
       </c>
       <c r="G25" s="214">
-        <v>1.226191</v>
+        <v>1.9897769999999999</v>
       </c>
     </row>
     <row r="26">
@@ -10785,22 +10785,22 @@
         <v>20</v>
       </c>
       <c r="B26" s="217">
-        <v>0.38366410000000001</v>
+        <v>0.53445279999999995</v>
       </c>
       <c r="C26" s="218">
-        <v>0.1128522</v>
+        <v>0.1794161</v>
       </c>
       <c r="D26" s="219">
-        <v>-3.2599999999999998</v>
+        <v>-1.8700000000000001</v>
       </c>
       <c r="E26" s="220">
-        <v>0.001</v>
+        <v>0.062</v>
       </c>
       <c r="F26" s="221">
-        <v>0.2155639</v>
+        <v>0.2767965</v>
       </c>
       <c r="G26" s="222">
-        <v>0.68285169999999995</v>
+        <v>1.031949</v>
       </c>
     </row>
     <row r="27">
@@ -10831,22 +10831,22 @@
         <v>23</v>
       </c>
       <c r="B28" s="233">
-        <v>0.61854469999999995</v>
+        <v>0.62077890000000002</v>
       </c>
       <c r="C28" s="234">
-        <v>0.056505</v>
+        <v>0.056664800000000001</v>
       </c>
       <c r="D28" s="235">
-        <v>-5.2599999999999998</v>
+        <v>-5.2199999999999998</v>
       </c>
       <c r="E28" s="236">
         <v>0</v>
       </c>
       <c r="F28" s="237">
-        <v>0.51714530000000003</v>
+        <v>0.51908589999999999</v>
       </c>
       <c r="G28" s="238">
-        <v>0.73982610000000004</v>
+        <v>0.74239449999999996</v>
       </c>
     </row>
     <row r="29">
@@ -10854,22 +10854,22 @@
         <v>24</v>
       </c>
       <c r="B29" s="241">
-        <v>0.94420899999999997</v>
+        <v>0.94324410000000003</v>
       </c>
       <c r="C29" s="242">
-        <v>0.0370184</v>
+        <v>0.036986100000000001</v>
       </c>
       <c r="D29" s="243">
-        <v>-1.46</v>
+        <v>-1.49</v>
       </c>
       <c r="E29" s="244">
-        <v>0.14299999999999999</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="F29" s="245">
-        <v>0.87437180000000003</v>
+        <v>0.87346840000000003</v>
       </c>
       <c r="G29" s="246">
-        <v>1.0196240000000001</v>
+        <v>1.018594</v>
       </c>
     </row>
     <row r="30">
@@ -10877,22 +10877,22 @@
         <v>25</v>
       </c>
       <c r="B30" s="249">
-        <v>0.3706199</v>
+        <v>0.37080049999999998</v>
       </c>
       <c r="C30" s="250">
-        <v>0.017372200000000001</v>
+        <v>0.017381299999999999</v>
       </c>
       <c r="D30" s="251">
-        <v>-21.18</v>
+        <v>-21.16</v>
       </c>
       <c r="E30" s="252">
         <v>0</v>
       </c>
       <c r="F30" s="253">
-        <v>0.33808820000000001</v>
+        <v>0.33825179999999999</v>
       </c>
       <c r="G30" s="254">
-        <v>0.40628180000000003</v>
+        <v>0.40648109999999999</v>
       </c>
     </row>
     <row r="31">
@@ -10900,22 +10900,22 @@
         <v>26</v>
       </c>
       <c r="B31" s="257">
-        <v>0.61722809999999995</v>
+        <v>0.61669490000000005</v>
       </c>
       <c r="C31" s="258">
-        <v>0.0221183</v>
+        <v>0.022101699999999999</v>
       </c>
       <c r="D31" s="259">
-        <v>-13.460000000000001</v>
+        <v>-13.49</v>
       </c>
       <c r="E31" s="260">
         <v>0</v>
       </c>
       <c r="F31" s="261">
-        <v>0.57536430000000005</v>
+        <v>0.57486280000000001</v>
       </c>
       <c r="G31" s="262">
-        <v>0.6621378</v>
+        <v>0.66157100000000002</v>
       </c>
     </row>
     <row r="32">
@@ -10923,22 +10923,22 @@
         <v>27</v>
       </c>
       <c r="B32" s="265">
-        <v>1.024848</v>
+        <v>1.024198</v>
       </c>
       <c r="C32" s="266">
-        <v>0.038185499999999997</v>
+        <v>0.038164200000000002</v>
       </c>
       <c r="D32" s="267">
-        <v>0.66000000000000003</v>
+        <v>0.64000000000000001</v>
       </c>
       <c r="E32" s="268">
-        <v>0.51000000000000001</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="F32" s="269">
-        <v>0.95267270000000004</v>
+        <v>0.95206329999999995</v>
       </c>
       <c r="G32" s="270">
-        <v>1.10249</v>
+        <v>1.1017969999999999</v>
       </c>
     </row>
     <row r="33">
@@ -10946,22 +10946,22 @@
         <v>28</v>
       </c>
       <c r="B33" s="273">
-        <v>1.3211790000000001</v>
+        <v>1.3181700000000001</v>
       </c>
       <c r="C33" s="274">
-        <v>0.0558938</v>
+        <v>0.055775400000000003</v>
       </c>
       <c r="D33" s="275">
-        <v>6.5800000000000001</v>
+        <v>6.5300000000000002</v>
       </c>
       <c r="E33" s="276">
         <v>0</v>
       </c>
       <c r="F33" s="277">
-        <v>1.216048</v>
+        <v>1.213263</v>
       </c>
       <c r="G33" s="278">
-        <v>1.4353990000000001</v>
+        <v>1.4321489999999999</v>
       </c>
     </row>
     <row r="34">
@@ -10969,22 +10969,22 @@
         <v>29</v>
       </c>
       <c r="B34" s="281">
-        <v>1.3510329999999999</v>
+        <v>1.344106</v>
       </c>
       <c r="C34" s="282">
-        <v>0.12576270000000001</v>
+        <v>0.12509809999999999</v>
       </c>
       <c r="D34" s="283">
-        <v>3.23</v>
+        <v>3.1800000000000002</v>
       </c>
       <c r="E34" s="284">
         <v>0.001</v>
       </c>
       <c r="F34" s="285">
-        <v>1.125721</v>
+        <v>1.119982</v>
       </c>
       <c r="G34" s="286">
-        <v>1.6214409999999999</v>
+        <v>1.6130819999999999</v>
       </c>
     </row>
     <row r="35">
@@ -10992,22 +10992,22 @@
         <v>30</v>
       </c>
       <c r="B35" s="289">
-        <v>0.75261800000000001</v>
+        <v>0.75188670000000002</v>
       </c>
       <c r="C35" s="290">
-        <v>0.046063100000000003</v>
+        <v>0.046022399999999998</v>
       </c>
       <c r="D35" s="291">
-        <v>-4.6399999999999997</v>
+        <v>-4.6600000000000001</v>
       </c>
       <c r="E35" s="292">
         <v>0</v>
       </c>
       <c r="F35" s="293">
-        <v>0.66754080000000005</v>
+        <v>0.66688499999999995</v>
       </c>
       <c r="G35" s="294">
-        <v>0.84853809999999996</v>
+        <v>0.84772270000000005</v>
       </c>
     </row>
     <row r="36">
@@ -11015,10 +11015,10 @@
         <v>31</v>
       </c>
       <c r="B36" s="297">
-        <v>0.6694888</v>
+        <v>0.66949479999999995</v>
       </c>
       <c r="C36" s="298">
-        <v>0.038833800000000002</v>
+        <v>0.038837400000000001</v>
       </c>
       <c r="D36" s="299">
         <v>-6.9199999999999999</v>
@@ -11027,10 +11027,10 @@
         <v>0</v>
       </c>
       <c r="F36" s="301">
-        <v>0.59754300000000005</v>
+        <v>0.59754269999999998</v>
       </c>
       <c r="G36" s="302">
-        <v>0.75009700000000001</v>
+        <v>0.75011079999999997</v>
       </c>
     </row>
     <row r="37">
@@ -11038,22 +11038,22 @@
         <v>32</v>
       </c>
       <c r="B37" s="305">
-        <v>0.57534320000000006</v>
+        <v>0.5705228</v>
       </c>
       <c r="C37" s="306">
-        <v>0.0357233</v>
+        <v>0.035507499999999997</v>
       </c>
       <c r="D37" s="307">
-        <v>-8.9000000000000004</v>
+        <v>-9.0199999999999996</v>
       </c>
       <c r="E37" s="308">
         <v>0</v>
       </c>
       <c r="F37" s="309">
-        <v>0.50941939999999997</v>
+        <v>0.50500639999999997</v>
       </c>
       <c r="G37" s="310">
-        <v>0.64979819999999999</v>
+        <v>0.64453870000000002</v>
       </c>
     </row>
     <row r="38">
@@ -11061,22 +11061,22 @@
         <v>33</v>
       </c>
       <c r="B38" s="313">
-        <v>0.7823618</v>
+        <v>0.78287119999999999</v>
       </c>
       <c r="C38" s="314">
-        <v>0.058772600000000001</v>
+        <v>0.058809100000000003</v>
       </c>
       <c r="D38" s="315">
-        <v>-3.27</v>
+        <v>-3.2599999999999998</v>
       </c>
       <c r="E38" s="316">
         <v>0.001</v>
       </c>
       <c r="F38" s="317">
-        <v>0.67524850000000003</v>
+        <v>0.67569120000000005</v>
       </c>
       <c r="G38" s="318">
-        <v>0.90646629999999995</v>
+        <v>0.90705239999999998</v>
       </c>
     </row>
     <row r="39">
@@ -11084,22 +11084,22 @@
         <v>34</v>
       </c>
       <c r="B39" s="321">
-        <v>1.0010699999999999</v>
+        <v>1.001849</v>
       </c>
       <c r="C39" s="322">
-        <v>0.0065053999999999997</v>
+        <v>0.0065202999999999997</v>
       </c>
       <c r="D39" s="323">
-        <v>0.16</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E39" s="324">
-        <v>0.869</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="F39" s="325">
-        <v>0.98840059999999996</v>
+        <v>0.98915030000000004</v>
       </c>
       <c r="G39" s="326">
-        <v>1.0139020000000001</v>
+        <v>1.01471</v>
       </c>
     </row>
     <row r="40">
@@ -11107,22 +11107,22 @@
         <v>35</v>
       </c>
       <c r="B40" s="329">
-        <v>0.91992850000000004</v>
+        <v>0.9206953</v>
       </c>
       <c r="C40" s="330">
-        <v>0.0842194</v>
+        <v>0.084301000000000001</v>
       </c>
       <c r="D40" s="331">
-        <v>-0.91000000000000003</v>
+        <v>-0.90000000000000002</v>
       </c>
       <c r="E40" s="332">
-        <v>0.36199999999999999</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="F40" s="333">
-        <v>0.76882349999999999</v>
+        <v>0.76944570000000001</v>
       </c>
       <c r="G40" s="334">
-        <v>1.100732</v>
+        <v>1.1016760000000001</v>
       </c>
     </row>
     <row r="41">
@@ -11130,22 +11130,22 @@
         <v>36</v>
       </c>
       <c r="B41" s="337">
-        <v>0.74411839999999996</v>
+        <v>0.74381160000000002</v>
       </c>
       <c r="C41" s="338">
-        <v>0.032703299999999998</v>
+        <v>0.032690400000000001</v>
       </c>
       <c r="D41" s="339">
-        <v>-6.7199999999999998</v>
+        <v>-6.7300000000000004</v>
       </c>
       <c r="E41" s="340">
         <v>0</v>
       </c>
       <c r="F41" s="341">
-        <v>0.68270419999999998</v>
+        <v>0.68242170000000002</v>
       </c>
       <c r="G41" s="342">
-        <v>0.81105729999999998</v>
+        <v>0.81072409999999995</v>
       </c>
     </row>
     <row r="42">
@@ -11153,22 +11153,22 @@
         <v>37</v>
       </c>
       <c r="B42" s="345">
-        <v>0.58266620000000002</v>
+        <v>0.58080270000000001</v>
       </c>
       <c r="C42" s="346">
-        <v>0.055627000000000003</v>
+        <v>0.0554826</v>
       </c>
       <c r="D42" s="347">
-        <v>-5.6600000000000001</v>
+        <v>-5.6900000000000004</v>
       </c>
       <c r="E42" s="348">
         <v>0</v>
       </c>
       <c r="F42" s="349">
-        <v>0.4832321</v>
+        <v>0.48163230000000001</v>
       </c>
       <c r="G42" s="350">
-        <v>0.70256070000000004</v>
+        <v>0.70039289999999999</v>
       </c>
     </row>
     <row r="43">
@@ -11176,22 +11176,22 @@
         <v>38</v>
       </c>
       <c r="B43" s="353">
-        <v>0.66170439999999997</v>
+        <v>0.66202450000000002</v>
       </c>
       <c r="C43" s="354">
-        <v>0.039001500000000001</v>
+        <v>0.039021899999999998</v>
       </c>
       <c r="D43" s="355">
-        <v>-7.0099999999999998</v>
+        <v>-7</v>
       </c>
       <c r="E43" s="356">
         <v>0</v>
       </c>
       <c r="F43" s="357">
-        <v>0.58951310000000001</v>
+        <v>0.58979539999999997</v>
       </c>
       <c r="G43" s="358">
-        <v>0.74273630000000002</v>
+        <v>0.74309910000000001</v>
       </c>
     </row>
     <row r="44">
@@ -11199,10 +11199,10 @@
         <v>39</v>
       </c>
       <c r="B44" s="361">
-        <v>0.65550010000000003</v>
+        <v>0.65536640000000002</v>
       </c>
       <c r="C44" s="362">
-        <v>0.037522699999999999</v>
+        <v>0.037515899999999998</v>
       </c>
       <c r="D44" s="363">
         <v>-7.3799999999999999</v>
@@ -11211,10 +11211,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="365">
-        <v>0.58593249999999997</v>
+        <v>0.58581139999999998</v>
       </c>
       <c r="G44" s="366">
-        <v>0.73332739999999996</v>
+        <v>0.73317980000000005</v>
       </c>
     </row>
     <row r="45">
@@ -11222,22 +11222,22 @@
         <v>40</v>
       </c>
       <c r="B45" s="369">
-        <v>0.51033649999999997</v>
+        <v>0.51136119999999996</v>
       </c>
       <c r="C45" s="370">
-        <v>0.1985391</v>
+        <v>0.19894770000000001</v>
       </c>
       <c r="D45" s="371">
-        <v>-1.73</v>
+        <v>-1.72</v>
       </c>
       <c r="E45" s="372">
-        <v>0.084000000000000005</v>
+        <v>0.085000000000000006</v>
       </c>
       <c r="F45" s="373">
-        <v>0.23807229999999999</v>
+        <v>0.23854120000000001</v>
       </c>
       <c r="G45" s="374">
-        <v>1.0939669999999999</v>
+        <v>1.096206</v>
       </c>
     </row>
     <row r="46">
@@ -11245,22 +11245,22 @@
         <v>41</v>
       </c>
       <c r="B46" s="377">
-        <v>1.258014</v>
+        <v>1.2574799999999999</v>
       </c>
       <c r="C46" s="378">
-        <v>0.0314293</v>
+        <v>0.031416199999999998</v>
       </c>
       <c r="D46" s="379">
-        <v>9.1899999999999995</v>
+        <v>9.1699999999999999</v>
       </c>
       <c r="E46" s="380">
         <v>0</v>
       </c>
       <c r="F46" s="381">
-        <v>1.1978979999999999</v>
+        <v>1.1973879999999999</v>
       </c>
       <c r="G46" s="382">
-        <v>1.321148</v>
+        <v>1.320587</v>
       </c>
     </row>
     <row r="47">
@@ -11268,22 +11268,22 @@
         <v>42</v>
       </c>
       <c r="B47" s="385">
-        <v>0.88331879999999996</v>
+        <v>0.8840266</v>
       </c>
       <c r="C47" s="386">
-        <v>0.0133797</v>
+        <v>0.013392899999999999</v>
       </c>
       <c r="D47" s="387">
-        <v>-8.1899999999999995</v>
+        <v>-8.1400000000000006</v>
       </c>
       <c r="E47" s="388">
         <v>0</v>
       </c>
       <c r="F47" s="389">
-        <v>0.85748060000000004</v>
+        <v>0.8581628</v>
       </c>
       <c r="G47" s="390">
-        <v>0.90993559999999996</v>
+        <v>0.91066979999999997</v>
       </c>
     </row>
     <row r="48">
@@ -11291,10 +11291,10 @@
         <v>43</v>
       </c>
       <c r="B48" s="393">
-        <v>0.77317499999999995</v>
+        <v>0.77310480000000004</v>
       </c>
       <c r="C48" s="394">
-        <v>0.029949400000000001</v>
+        <v>0.029943899999999999</v>
       </c>
       <c r="D48" s="395">
         <v>-6.6399999999999997</v>
@@ -11303,10 +11303,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="397">
-        <v>0.71664810000000001</v>
+        <v>0.71658820000000001</v>
       </c>
       <c r="G48" s="398">
-        <v>0.83416049999999997</v>
+        <v>0.83407889999999996</v>
       </c>
     </row>
     <row r="49">
@@ -11314,22 +11314,22 @@
         <v>44</v>
       </c>
       <c r="B49" s="401">
-        <v>0.8259282</v>
+        <v>0.82659609999999995</v>
       </c>
       <c r="C49" s="402">
-        <v>0.044939100000000003</v>
+        <v>0.044977900000000001</v>
       </c>
       <c r="D49" s="403">
-        <v>-3.5099999999999998</v>
+        <v>-3.5</v>
       </c>
       <c r="E49" s="404">
         <v>0</v>
       </c>
       <c r="F49" s="405">
-        <v>0.74238309999999996</v>
+        <v>0.74297919999999995</v>
       </c>
       <c r="G49" s="406">
-        <v>0.9188752</v>
+        <v>0.91962350000000004</v>
       </c>
     </row>
     <row r="50">
@@ -11337,22 +11337,22 @@
         <v>45</v>
       </c>
       <c r="B50" s="409">
-        <v>0.72623340000000003</v>
+        <v>0.72591669999999997</v>
       </c>
       <c r="C50" s="410">
-        <v>0.019874699999999999</v>
+        <v>0.019868400000000001</v>
       </c>
       <c r="D50" s="411">
-        <v>-11.69</v>
+        <v>-11.699999999999999</v>
       </c>
       <c r="E50" s="412">
         <v>0</v>
       </c>
       <c r="F50" s="413">
-        <v>0.68830590000000003</v>
+        <v>0.68800130000000004</v>
       </c>
       <c r="G50" s="414">
-        <v>0.76625069999999995</v>
+        <v>0.76592150000000003</v>
       </c>
     </row>
     <row r="51">
@@ -11360,10 +11360,10 @@
         <v>46</v>
       </c>
       <c r="B51" s="417">
-        <v>1.091251</v>
+        <v>1.0912660000000001</v>
       </c>
       <c r="C51" s="418">
-        <v>0.074403399999999995</v>
+        <v>0.074395199999999995</v>
       </c>
       <c r="D51" s="419">
         <v>1.28</v>
@@ -11372,10 +11372,10 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="F51" s="421">
-        <v>0.95474680000000001</v>
+        <v>0.95477599999999996</v>
       </c>
       <c r="G51" s="422">
-        <v>1.2472719999999999</v>
+        <v>1.247268</v>
       </c>
     </row>
     <row r="52">
@@ -11383,22 +11383,22 @@
         <v>47</v>
       </c>
       <c r="B52" s="425">
-        <v>0.80988649999999995</v>
+        <v>0.8106778</v>
       </c>
       <c r="C52" s="426">
-        <v>0.043495800000000001</v>
+        <v>0.043542200000000003</v>
       </c>
       <c r="D52" s="427">
-        <v>-3.9300000000000002</v>
+        <v>-3.9100000000000001</v>
       </c>
       <c r="E52" s="428">
         <v>0</v>
       </c>
       <c r="F52" s="429">
-        <v>0.7289696</v>
+        <v>0.72967499999999996</v>
       </c>
       <c r="G52" s="430">
-        <v>0.89978519999999995</v>
+        <v>0.9006729</v>
       </c>
     </row>
     <row r="53">
@@ -11406,22 +11406,22 @@
         <v>48</v>
       </c>
       <c r="B53" s="433">
-        <v>0.97011939999999997</v>
+        <v>0.9698909</v>
       </c>
       <c r="C53" s="434">
-        <v>0.024922099999999999</v>
+        <v>0.0249172</v>
       </c>
       <c r="D53" s="435">
-        <v>-1.1799999999999999</v>
+        <v>-1.19</v>
       </c>
       <c r="E53" s="436">
-        <v>0.23799999999999999</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="F53" s="437">
-        <v>0.92248240000000004</v>
+        <v>0.92226319999999995</v>
       </c>
       <c r="G53" s="438">
-        <v>1.020216</v>
+        <v>1.0199780000000001</v>
       </c>
     </row>
     <row r="54">
@@ -11429,22 +11429,22 @@
         <v>49</v>
       </c>
       <c r="B54" s="441">
-        <v>0.8355688</v>
+        <v>0.83589780000000002</v>
       </c>
       <c r="C54" s="442">
-        <v>0.0226137</v>
+        <v>0.0226243</v>
       </c>
       <c r="D54" s="443">
-        <v>-6.6399999999999997</v>
+        <v>-6.6200000000000001</v>
       </c>
       <c r="E54" s="444">
         <v>0</v>
       </c>
       <c r="F54" s="445">
-        <v>0.79240180000000005</v>
+        <v>0.79271069999999999</v>
       </c>
       <c r="G54" s="446">
-        <v>0.88108739999999997</v>
+        <v>0.88143780000000005</v>
       </c>
     </row>
     <row r="55">
@@ -11475,22 +11475,22 @@
         <v>52</v>
       </c>
       <c r="B56" s="457">
-        <v>0.7207346</v>
+        <v>0.7216747</v>
       </c>
       <c r="C56" s="458">
-        <v>0.068832000000000004</v>
+        <v>0.068934200000000001</v>
       </c>
       <c r="D56" s="459">
-        <v>-3.4300000000000002</v>
+        <v>-3.4100000000000001</v>
       </c>
       <c r="E56" s="460">
         <v>0.001</v>
       </c>
       <c r="F56" s="461">
-        <v>0.59770029999999996</v>
+        <v>0.59845970000000004</v>
       </c>
       <c r="G56" s="462">
-        <v>0.86909510000000001</v>
+        <v>0.87025790000000003</v>
       </c>
     </row>
     <row r="57">
@@ -11498,22 +11498,22 @@
         <v>53</v>
       </c>
       <c r="B57" s="465">
-        <v>0.80580439999999998</v>
+        <v>0.80537550000000002</v>
       </c>
       <c r="C57" s="466">
-        <v>0.081165200000000007</v>
+        <v>0.081134200000000004</v>
       </c>
       <c r="D57" s="467">
-        <v>-2.1400000000000001</v>
+        <v>-2.1499999999999999</v>
       </c>
       <c r="E57" s="468">
         <v>0.032000000000000001</v>
       </c>
       <c r="F57" s="469">
-        <v>0.66144199999999998</v>
+        <v>0.66107020000000005</v>
       </c>
       <c r="G57" s="470">
-        <v>0.98167439999999995</v>
+        <v>0.98118110000000003</v>
       </c>
     </row>
     <row r="58">
@@ -11521,22 +11521,22 @@
         <v>54</v>
       </c>
       <c r="B58" s="473">
-        <v>0.77043819999999996</v>
+        <v>0.77167459999999999</v>
       </c>
       <c r="C58" s="474">
-        <v>0.067723800000000001</v>
+        <v>0.067846299999999998</v>
       </c>
       <c r="D58" s="475">
-        <v>-2.9700000000000002</v>
+        <v>-2.9500000000000002</v>
       </c>
       <c r="E58" s="476">
         <v>0.0030000000000000001</v>
       </c>
       <c r="F58" s="477">
-        <v>0.64850699999999995</v>
+        <v>0.64952489999999996</v>
       </c>
       <c r="G58" s="478">
-        <v>0.91529459999999996</v>
+        <v>0.91679580000000005</v>
       </c>
     </row>
     <row r="59">
@@ -11544,22 +11544,22 @@
         <v>55</v>
       </c>
       <c r="B59" s="481">
-        <v>1.4161280000000001</v>
+        <v>1.4178489999999999</v>
       </c>
       <c r="C59" s="482">
-        <v>0.1210027</v>
+        <v>0.1211749</v>
       </c>
       <c r="D59" s="483">
-        <v>4.0700000000000003</v>
+        <v>4.0899999999999999</v>
       </c>
       <c r="E59" s="484">
         <v>0</v>
       </c>
       <c r="F59" s="485">
-        <v>1.1977629999999999</v>
+        <v>1.199176</v>
       </c>
       <c r="G59" s="486">
-        <v>1.6743049999999999</v>
+        <v>1.6763969999999999</v>
       </c>
     </row>
     <row r="60">
@@ -11567,22 +11567,22 @@
         <v>56</v>
       </c>
       <c r="B60" s="489">
-        <v>1.7580359999999999</v>
+        <v>1.762564</v>
       </c>
       <c r="C60" s="490">
-        <v>1.7752589999999999</v>
+        <v>1.7799590000000001</v>
       </c>
       <c r="D60" s="491">
         <v>0.56000000000000005</v>
       </c>
       <c r="E60" s="492">
-        <v>0.57599999999999996</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="F60" s="493">
-        <v>0.2429337</v>
+        <v>0.24352470000000001</v>
       </c>
       <c r="G60" s="494">
-        <v>12.72237</v>
+        <v>12.75695</v>
       </c>
     </row>
     <row r="61">
@@ -11590,22 +11590,22 @@
         <v>57</v>
       </c>
       <c r="B61" s="497">
-        <v>0.75599850000000002</v>
+        <v>0.75496629999999998</v>
       </c>
       <c r="C61" s="498">
-        <v>0.032480200000000001</v>
+        <v>0.0324512</v>
       </c>
       <c r="D61" s="499">
-        <v>-6.5099999999999998</v>
+        <v>-6.54</v>
       </c>
       <c r="E61" s="500">
         <v>0</v>
       </c>
       <c r="F61" s="501">
-        <v>0.69494500000000003</v>
+        <v>0.69396849999999999</v>
       </c>
       <c r="G61" s="502">
-        <v>0.82241569999999997</v>
+        <v>0.82132559999999999</v>
       </c>
     </row>
     <row r="62">
@@ -11613,22 +11613,22 @@
         <v>58</v>
       </c>
       <c r="B62" s="505">
-        <v>0.89424119999999996</v>
+        <v>0.8953122</v>
       </c>
       <c r="C62" s="506">
-        <v>0.040978000000000001</v>
+        <v>0.0410359</v>
       </c>
       <c r="D62" s="507">
-        <v>-2.44</v>
+        <v>-2.4100000000000001</v>
       </c>
       <c r="E62" s="508">
-        <v>0.014999999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="F62" s="509">
-        <v>0.81742680000000001</v>
+        <v>0.81839010000000001</v>
       </c>
       <c r="G62" s="510">
-        <v>0.97827379999999997</v>
+        <v>0.97946429999999996</v>
       </c>
     </row>
     <row r="63">
@@ -11636,22 +11636,22 @@
         <v>59</v>
       </c>
       <c r="B63" s="513">
-        <v>1.056961</v>
+        <v>1.0554969999999999</v>
       </c>
       <c r="C63" s="514">
-        <v>0.039246200000000002</v>
+        <v>0.039192900000000003</v>
       </c>
       <c r="D63" s="515">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="E63" s="516">
-        <v>0.13600000000000001</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="F63" s="517">
-        <v>0.98277230000000004</v>
+        <v>0.98140870000000002</v>
       </c>
       <c r="G63" s="518">
-        <v>1.1367499999999999</v>
+        <v>1.135178</v>
       </c>
     </row>
     <row r="64">
@@ -11659,22 +11659,22 @@
         <v>60</v>
       </c>
       <c r="B64" s="521">
-        <v>1.493479</v>
+        <v>1.4941279999999999</v>
       </c>
       <c r="C64" s="522">
-        <v>0.1229049</v>
+        <v>0.1229504</v>
       </c>
       <c r="D64" s="523">
-        <v>4.8700000000000001</v>
+        <v>4.8799999999999999</v>
       </c>
       <c r="E64" s="524">
         <v>0</v>
       </c>
       <c r="F64" s="525">
-        <v>1.271013</v>
+        <v>1.271579</v>
       </c>
       <c r="G64" s="526">
-        <v>1.754883</v>
+        <v>1.755628</v>
       </c>
     </row>
     <row r="65">
@@ -11682,22 +11682,22 @@
         <v>61</v>
       </c>
       <c r="B65" s="529">
-        <v>1.1506179999999999</v>
+        <v>1.152841</v>
       </c>
       <c r="C65" s="530">
-        <v>0.15660560000000001</v>
+        <v>0.15695619999999999</v>
       </c>
       <c r="D65" s="531">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="E65" s="532">
-        <v>0.30299999999999999</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="F65" s="533">
-        <v>0.88120679999999996</v>
+        <v>0.88283719999999999</v>
       </c>
       <c r="G65" s="534">
-        <v>1.5023960000000001</v>
+        <v>1.505422</v>
       </c>
     </row>
     <row r="66">
@@ -11705,22 +11705,22 @@
         <v>62</v>
       </c>
       <c r="B66" s="537">
-        <v>1.4314180000000001</v>
+        <v>1.4327350000000001</v>
       </c>
       <c r="C66" s="538">
-        <v>1.915135</v>
+        <v>1.9158919999999999</v>
       </c>
       <c r="D66" s="539">
         <v>0.27000000000000002</v>
       </c>
       <c r="E66" s="540">
-        <v>0.78900000000000003</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="F66" s="541">
-        <v>0.1039727</v>
+        <v>0.1042115</v>
       </c>
       <c r="G66" s="542">
-        <v>19.706679999999999</v>
+        <v>19.69772</v>
       </c>
     </row>
     <row r="67">
@@ -11728,22 +11728,22 @@
         <v>63</v>
       </c>
       <c r="B67" s="545">
-        <v>1.036089</v>
+        <v>1.036303</v>
       </c>
       <c r="C67" s="546">
-        <v>0.062768900000000002</v>
+        <v>0.062786999999999996</v>
       </c>
       <c r="D67" s="547">
         <v>0.58999999999999997</v>
       </c>
       <c r="E67" s="548">
-        <v>0.55800000000000005</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="F67" s="549">
-        <v>0.92008699999999999</v>
+        <v>0.92026859999999999</v>
       </c>
       <c r="G67" s="550">
-        <v>1.166715</v>
+        <v>1.166968</v>
       </c>
     </row>
     <row r="68">
@@ -11751,22 +11751,22 @@
         <v>64</v>
       </c>
       <c r="B68" s="553">
-        <v>1.38398</v>
+        <v>1.382368</v>
       </c>
       <c r="C68" s="554">
-        <v>0.085350099999999998</v>
+        <v>0.085228999999999999</v>
       </c>
       <c r="D68" s="555">
-        <v>5.2699999999999996</v>
+        <v>5.25</v>
       </c>
       <c r="E68" s="556">
         <v>0</v>
       </c>
       <c r="F68" s="557">
-        <v>1.2264120000000001</v>
+        <v>1.22502</v>
       </c>
       <c r="G68" s="558">
-        <v>1.561793</v>
+        <v>1.5599259999999999</v>
       </c>
     </row>
     <row r="69">
@@ -11774,22 +11774,22 @@
         <v>65</v>
       </c>
       <c r="B69" s="561">
-        <v>0.93648100000000001</v>
+        <v>0.93274429999999997</v>
       </c>
       <c r="C69" s="562">
-        <v>0.0772785</v>
+        <v>0.076957700000000004</v>
       </c>
       <c r="D69" s="563">
-        <v>-0.80000000000000004</v>
+        <v>-0.83999999999999997</v>
       </c>
       <c r="E69" s="564">
-        <v>0.42599999999999999</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="F69" s="565">
-        <v>0.79663200000000001</v>
+        <v>0.79347400000000001</v>
       </c>
       <c r="G69" s="566">
-        <v>1.100881</v>
+        <v>1.0964590000000001</v>
       </c>
     </row>
     <row r="70">
@@ -11797,22 +11797,22 @@
         <v>66</v>
       </c>
       <c r="B70" s="569">
-        <v>0.24283179999999999</v>
+        <v>0.24351680000000001</v>
       </c>
       <c r="C70" s="570">
-        <v>0.1393258</v>
+        <v>0.1397899</v>
       </c>
       <c r="D70" s="571">
-        <v>-2.4700000000000002</v>
+        <v>-2.46</v>
       </c>
       <c r="E70" s="572">
         <v>0.014</v>
       </c>
       <c r="F70" s="573">
-        <v>0.078872399999999995</v>
+        <v>0.079049599999999998</v>
       </c>
       <c r="G70" s="574">
-        <v>0.74762910000000005</v>
+        <v>0.75016700000000003</v>
       </c>
     </row>
     <row r="71">
@@ -11820,10 +11820,10 @@
         <v>67</v>
       </c>
       <c r="B71" s="577">
-        <v>1.5988100000000001</v>
+        <v>1.5965020000000001</v>
       </c>
       <c r="C71" s="578">
-        <v>0.21047370000000001</v>
+        <v>0.21008199999999999</v>
       </c>
       <c r="D71" s="579">
         <v>3.5600000000000001</v>
@@ -11832,10 +11832,10 @@
         <v>0</v>
       </c>
       <c r="F71" s="581">
-        <v>1.2352110000000001</v>
+        <v>1.2335609999999999</v>
       </c>
       <c r="G71" s="582">
-        <v>2.0694379999999999</v>
+        <v>2.066227</v>
       </c>
     </row>
     <row r="72">
@@ -11843,22 +11843,22 @@
         <v>68</v>
       </c>
       <c r="B72" s="585">
-        <v>1.217894</v>
+        <v>1.219797</v>
       </c>
       <c r="C72" s="586">
-        <v>0.19734779999999999</v>
+        <v>0.19766149999999999</v>
       </c>
       <c r="D72" s="587">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="E72" s="588">
-        <v>0.224</v>
+        <v>0.22</v>
       </c>
       <c r="F72" s="589">
-        <v>0.88650359999999995</v>
+        <v>0.88788120000000004</v>
       </c>
       <c r="G72" s="590">
-        <v>1.673163</v>
+        <v>1.675792</v>
       </c>
     </row>
     <row r="73">
@@ -11866,22 +11866,22 @@
         <v>69</v>
       </c>
       <c r="B73" s="593">
-        <v>0.85905169999999997</v>
+        <v>0.85960919999999996</v>
       </c>
       <c r="C73" s="594">
-        <v>0.070293099999999997</v>
+        <v>0.070324899999999996</v>
       </c>
       <c r="D73" s="595">
-        <v>-1.8600000000000001</v>
+        <v>-1.8500000000000001</v>
       </c>
       <c r="E73" s="596">
-        <v>0.063</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="F73" s="597">
-        <v>0.73175979999999996</v>
+        <v>0.73225779999999996</v>
       </c>
       <c r="G73" s="598">
-        <v>1.008486</v>
+        <v>1.009109</v>
       </c>
     </row>
     <row r="74">
@@ -11889,10 +11889,10 @@
         <v>70</v>
       </c>
       <c r="B74" s="601">
-        <v>1.34568</v>
+        <v>1.345596</v>
       </c>
       <c r="C74" s="602">
-        <v>0.1403526</v>
+        <v>0.1403732</v>
       </c>
       <c r="D74" s="603">
         <v>2.8500000000000001</v>
@@ -11901,10 +11901,10 @@
         <v>0.0040000000000000001</v>
       </c>
       <c r="F74" s="605">
-        <v>1.096889</v>
+        <v>1.0967739999999999</v>
       </c>
       <c r="G74" s="606">
-        <v>1.650901</v>
+        <v>1.650868</v>
       </c>
     </row>
     <row r="75">
@@ -11912,22 +11912,22 @@
         <v>71</v>
       </c>
       <c r="B75" s="609">
-        <v>0.98489990000000005</v>
+        <v>0.99067079999999996</v>
       </c>
       <c r="C75" s="610">
-        <v>0.034149600000000002</v>
+        <v>0.034451900000000001</v>
       </c>
       <c r="D75" s="611">
-        <v>-0.44</v>
+        <v>-0.27000000000000002</v>
       </c>
       <c r="E75" s="612">
-        <v>0.66100000000000003</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="F75" s="613">
-        <v>0.9201916</v>
+        <v>0.92539610000000005</v>
       </c>
       <c r="G75" s="614">
-        <v>1.0541579999999999</v>
+        <v>1.0605500000000001</v>
       </c>
     </row>
     <row r="76">
@@ -11935,22 +11935,22 @@
         <v>72</v>
       </c>
       <c r="B76" s="617">
-        <v>1.0699559999999999</v>
+        <v>1.0842270000000001</v>
       </c>
       <c r="C76" s="618">
-        <v>0.090632500000000005</v>
+        <v>0.092086899999999999</v>
       </c>
       <c r="D76" s="619">
-        <v>0.80000000000000004</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="E76" s="620">
-        <v>0.42499999999999999</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="F76" s="621">
-        <v>0.90628240000000004</v>
+        <v>0.91796239999999996</v>
       </c>
       <c r="G76" s="622">
-        <v>1.26319</v>
+        <v>1.2806059999999999</v>
       </c>
     </row>
     <row r="77">
@@ -11958,22 +11958,22 @@
         <v>73</v>
       </c>
       <c r="B77" s="625">
-        <v>0.83623409999999998</v>
+        <v>0.83378140000000001</v>
       </c>
       <c r="C77" s="626">
-        <v>0.0337463</v>
+        <v>0.033652799999999997</v>
       </c>
       <c r="D77" s="627">
-        <v>-4.4299999999999997</v>
+        <v>-4.5</v>
       </c>
       <c r="E77" s="628">
         <v>0</v>
       </c>
       <c r="F77" s="629">
-        <v>0.77264060000000001</v>
+        <v>0.77036450000000001</v>
       </c>
       <c r="G77" s="630">
-        <v>0.90506180000000003</v>
+        <v>0.90241879999999997</v>
       </c>
     </row>
     <row r="78">
@@ -11981,22 +11981,22 @@
         <v>74</v>
       </c>
       <c r="B78" s="633">
-        <v>1.353286</v>
+        <v>1.3566720000000001</v>
       </c>
       <c r="C78" s="634">
-        <v>0.1866082</v>
+        <v>0.1870851</v>
       </c>
       <c r="D78" s="635">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="E78" s="636">
-        <v>0.028000000000000001</v>
+        <v>0.027</v>
       </c>
       <c r="F78" s="637">
-        <v>1.032797</v>
+        <v>1.0353669999999999</v>
       </c>
       <c r="G78" s="638">
-        <v>1.773226</v>
+        <v>1.7776879999999999</v>
       </c>
     </row>
     <row r="79">
@@ -12004,22 +12004,22 @@
         <v>75</v>
       </c>
       <c r="B79" s="641">
-        <v>0.78610849999999999</v>
+        <v>0.78661049999999999</v>
       </c>
       <c r="C79" s="642">
-        <v>0.027741399999999999</v>
+        <v>0.027761999999999999</v>
       </c>
       <c r="D79" s="643">
-        <v>-6.8200000000000003</v>
+        <v>-6.7999999999999998</v>
       </c>
       <c r="E79" s="644">
         <v>0</v>
       </c>
       <c r="F79" s="645">
-        <v>0.73357399999999995</v>
+        <v>0.7340373</v>
       </c>
       <c r="G79" s="646">
-        <v>0.84240510000000002</v>
+        <v>0.84294910000000001</v>
       </c>
     </row>
     <row r="80">
@@ -12027,22 +12027,22 @@
         <v>76</v>
       </c>
       <c r="B80" s="656">
-        <v>4.4541620000000002</v>
+        <v>3.0528580000000001</v>
       </c>
       <c r="C80" s="657">
-        <v>1.84239</v>
+        <v>1.379583</v>
       </c>
       <c r="D80" s="658">
-        <v>3.6099999999999999</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="E80" s="659">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="F80" s="660">
-        <v>1.98007</v>
+        <v>1.259069</v>
       </c>
       <c r="G80" s="661">
-        <v>10.01962</v>
+        <v>7.4022490000000003</v>
       </c>
     </row>
   </sheetData>
